--- a/KG/Batch_KG/sample_data/class_level_data_1.xlsx
+++ b/KG/Batch_KG/sample_data/class_level_data_1.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Iris\practice\GenAI\code\Batch_KG\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B96BB433-8EDD-4775-889F-F2BF26614EC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1593B267-6CFE-4DF5-8F2B-C85100CD29B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JobGroups" sheetId="1" r:id="rId1"/>
-    <sheet name="Jobs" sheetId="2" r:id="rId2"/>
+    <sheet name="Jobs" sheetId="2" state="hidden" r:id="rId2"/>
     <sheet name="AssociatedJobs" sheetId="17" r:id="rId3"/>
     <sheet name="Resources" sheetId="5" r:id="rId4"/>
     <sheet name="JobContext" sheetId="11" r:id="rId5"/>
     <sheet name="ResourceDependency" sheetId="6" r:id="rId6"/>
     <sheet name="SLAs" sheetId="8" r:id="rId7"/>
-    <sheet name="Calendar" sheetId="9" r:id="rId8"/>
-    <sheet name="DataInteraction_v2" sheetId="15" r:id="rId9"/>
-    <sheet name="Tags" sheetId="16" r:id="rId10"/>
-    <sheet name="DataInteraction_v1" sheetId="14" r:id="rId11"/>
-    <sheet name="AssociateCalendar" sheetId="12" r:id="rId12"/>
-    <sheet name="Holidays" sheetId="10" r:id="rId13"/>
+    <sheet name="CalendarPatterns" sheetId="9" r:id="rId8"/>
+    <sheet name="JobRules" sheetId="18" r:id="rId9"/>
+    <sheet name="DataInteraction_v2" sheetId="15" state="hidden" r:id="rId10"/>
+    <sheet name="JobRulesAssociation" sheetId="12" r:id="rId11"/>
+    <sheet name="Holidays" sheetId="10" r:id="rId12"/>
+    <sheet name="Tags" sheetId="16" r:id="rId13"/>
+    <sheet name="DataInteraction_v1" sheetId="14" state="hidden" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="558">
   <si>
     <t>id</t>
   </si>
@@ -200,9 +201,6 @@
     <t>contextForEntityId</t>
   </si>
   <si>
-    <t>policy</t>
-  </si>
-  <si>
     <t>time</t>
   </si>
   <si>
@@ -290,126 +288,15 @@
     <t>SLA_End of Day Processing</t>
   </si>
   <si>
-    <t>finish_by_time</t>
-  </si>
-  <si>
     <t>JobGroup</t>
   </si>
   <si>
-    <t>blockedDays</t>
-  </si>
-  <si>
-    <t>startTime</t>
-  </si>
-  <si>
-    <t>endTime</t>
-  </si>
-  <si>
-    <t>DAY_OF_WEEK</t>
-  </si>
-  <si>
-    <t>['SATURDAY', 'SUNDAY']</t>
-  </si>
-  <si>
-    <t>TIME_WINDOW</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
     <t>HOLIDAY</t>
   </si>
   <si>
     <t>date</t>
   </si>
   <si>
-    <t>HOLIDAY_001</t>
-  </si>
-  <si>
-    <t>New Year 2024</t>
-  </si>
-  <si>
-    <t>2024-11-01</t>
-  </si>
-  <si>
-    <t>HOLIDAY_002</t>
-  </si>
-  <si>
-    <t>Thanksgiving 2024</t>
-  </si>
-  <si>
-    <t>2024-11-28</t>
-  </si>
-  <si>
-    <t>HOLIDAY_003</t>
-  </si>
-  <si>
-    <t>Christmas 2024</t>
-  </si>
-  <si>
-    <t>2024-12-25</t>
-  </si>
-  <si>
-    <t>HOLIDAY_004</t>
-  </si>
-  <si>
-    <t>New Year 2025</t>
-  </si>
-  <si>
-    <t>2025-01-01</t>
-  </si>
-  <si>
-    <t>HOLIDAY_005</t>
-  </si>
-  <si>
-    <t>Independence Day 2025</t>
-  </si>
-  <si>
-    <t>2025-07-04</t>
-  </si>
-  <si>
-    <t>HOLIDAY_006</t>
-  </si>
-  <si>
-    <t>Thanksgiving 2025</t>
-  </si>
-  <si>
-    <t>2025-11-27</t>
-  </si>
-  <si>
-    <t>HOLIDAY_007</t>
-  </si>
-  <si>
-    <t>Christmas 2025</t>
-  </si>
-  <si>
-    <t>2025-12-25</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
     <t>ctx_0002</t>
   </si>
   <si>
@@ -449,69 +336,24 @@
     <t>Y</t>
   </si>
   <si>
-    <t>calendarId</t>
-  </si>
-  <si>
     <t>Weekend Days</t>
   </si>
   <si>
-    <t>CAL_003</t>
-  </si>
-  <si>
-    <t>CAL_002</t>
-  </si>
-  <si>
-    <t>CAL_001</t>
-  </si>
-  <si>
     <t>Business Hours</t>
   </si>
   <si>
-    <t>Time window based calendar for 06:00 to 22:00</t>
-  </si>
-  <si>
-    <t>Calendar created for Global Holidays in US</t>
-  </si>
-  <si>
     <t>Global Holidays in US</t>
   </si>
   <si>
-    <t>CAL_004</t>
-  </si>
-  <si>
     <t>Month End Day</t>
   </si>
   <si>
-    <t>Calendar created for last day of the Month</t>
-  </si>
-  <si>
-    <t>DAY_OF_MONTH</t>
-  </si>
-  <si>
-    <t>CAL_005</t>
-  </si>
-  <si>
     <t>Month Start Day</t>
   </si>
   <si>
-    <t>Calendar created for first day of the Month</t>
-  </si>
-  <si>
-    <t>CAL_006</t>
-  </si>
-  <si>
     <t>Week Days</t>
   </si>
   <si>
-    <t>['MONDAY', 'TUESDAY','WEDNESDAY','THURSDAY','FRIDAY']</t>
-  </si>
-  <si>
-    <t>Calendar marking the weekdays</t>
-  </si>
-  <si>
-    <t>Calendar marking weekends such as SATURDAY and SUNDAY</t>
-  </si>
-  <si>
     <t>Allowed</t>
   </si>
   <si>
@@ -650,12 +492,6 @@
     <t>SLA_0013</t>
   </si>
   <si>
-    <t>duration_less_than</t>
-  </si>
-  <si>
-    <t>duration_relative</t>
-  </si>
-  <si>
     <t>relativeEntityId</t>
   </si>
   <si>
@@ -671,9 +507,6 @@
     <t>SLA_Account Balance Calculation Resource</t>
   </si>
   <si>
-    <t>available_by_time</t>
-  </si>
-  <si>
     <t>06:15</t>
   </si>
   <si>
@@ -920,9 +753,6 @@
     <t>Tag for input files</t>
   </si>
   <si>
-    <t>[TAG_CUSTOMER_DATA]</t>
-  </si>
-  <si>
     <t>[TAG_CUSTOMER_AGGREGATE_DATA]</t>
   </si>
   <si>
@@ -1019,12 +849,6 @@
     <t>SLA_0014</t>
   </si>
   <si>
-    <t>estimatedDurationMs</t>
-  </si>
-  <si>
-    <t>realSLA</t>
-  </si>
-  <si>
     <t>SLA_Mid Day Processing</t>
   </si>
   <si>
@@ -1248,13 +1072,664 @@
   </si>
   <si>
     <t>ORDER</t>
+  </si>
+  <si>
+    <t>CCAR_FS_TRIGGER</t>
+  </si>
+  <si>
+    <t>ctx_0033</t>
+  </si>
+  <si>
+    <t>[TAG_CUSTOMER_DATA,TAG_CUSTOMER_ACCOUNT_DATA]</t>
+  </si>
+  <si>
+    <t>US_2026_04</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>Juneteenth National Independence Day</t>
+  </si>
+  <si>
+    <t>US_2026_05</t>
+  </si>
+  <si>
+    <t>Independence Day (observed)</t>
+  </si>
+  <si>
+    <t>US_2026_06</t>
+  </si>
+  <si>
+    <t>Labor Day</t>
+  </si>
+  <si>
+    <t>US_2026_07</t>
+  </si>
+  <si>
+    <t>Columbus Day</t>
+  </si>
+  <si>
+    <t>US_2026_08</t>
+  </si>
+  <si>
+    <t>Veterans Day</t>
+  </si>
+  <si>
+    <t>US_2026_09</t>
+  </si>
+  <si>
+    <t>Thanksgiving Day</t>
+  </si>
+  <si>
+    <t>CA_2026_01</t>
+  </si>
+  <si>
+    <t>CA</t>
+  </si>
+  <si>
+    <t>Family Day</t>
+  </si>
+  <si>
+    <t>ALL_2026_01</t>
+  </si>
+  <si>
+    <t>ALL</t>
+  </si>
+  <si>
+    <t>New Year's Day</t>
+  </si>
+  <si>
+    <t>ALL_2026_02</t>
+  </si>
+  <si>
+    <t>Good Friday</t>
+  </si>
+  <si>
+    <t>ALL_2026_03</t>
+  </si>
+  <si>
+    <t>Easter Monday</t>
+  </si>
+  <si>
+    <t>ALL_2026_04</t>
+  </si>
+  <si>
+    <t>Christmas Day</t>
+  </si>
+  <si>
+    <t>ALL_2026_05</t>
+  </si>
+  <si>
+    <t>Boxing Day</t>
+  </si>
+  <si>
+    <t>US_2026_01</t>
+  </si>
+  <si>
+    <t>Martin Luther King Jr. Day</t>
+  </si>
+  <si>
+    <t>US_2026_02</t>
+  </si>
+  <si>
+    <t>Presidents' Day</t>
+  </si>
+  <si>
+    <t>US_2026_03</t>
+  </si>
+  <si>
+    <t>Memorial Day</t>
+  </si>
+  <si>
+    <t>CA_2026_02</t>
+  </si>
+  <si>
+    <t>Victoria Day</t>
+  </si>
+  <si>
+    <t>CA_2026_03</t>
+  </si>
+  <si>
+    <t>Canada Day</t>
+  </si>
+  <si>
+    <t>CA_2026_04</t>
+  </si>
+  <si>
+    <t>Civic Holiday</t>
+  </si>
+  <si>
+    <t>CA_2026_05</t>
+  </si>
+  <si>
+    <t>Labour Day</t>
+  </si>
+  <si>
+    <t>CA_2026_06</t>
+  </si>
+  <si>
+    <t>National Day for Truth and Reconciliation</t>
+  </si>
+  <si>
+    <t>CA_2026_07</t>
+  </si>
+  <si>
+    <t>CA_2026_08</t>
+  </si>
+  <si>
+    <t>Remembrance Day</t>
+  </si>
+  <si>
+    <t>region</t>
+  </si>
+  <si>
+    <t>patternId</t>
+  </si>
+  <si>
+    <t>matchExpression</t>
+  </si>
+  <si>
+    <t>evaluatorFn</t>
+  </si>
+  <si>
+    <t>isActive</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>PAT_NTH_DOW_MONTH</t>
+  </si>
+  <si>
+    <t>NTH_DOW_MONTH</t>
+  </si>
+  <si>
+    <t>Nth Day-of-Week in Month</t>
+  </si>
+  <si>
+    <t>nth_dow_month</t>
+  </si>
+  <si>
+    <t>PAT_NTH_DOWS_MONTH</t>
+  </si>
+  <si>
+    <t>NTH_DOWS_MONTH</t>
+  </si>
+  <si>
+    <t>Nth Days-of-Week in Month</t>
+  </si>
+  <si>
+    <t>nth_dows_month</t>
+  </si>
+  <si>
+    <t>PAT_NTH_DOM</t>
+  </si>
+  <si>
+    <t>NTH_DOM</t>
+  </si>
+  <si>
+    <t>Nth Day-of-Month</t>
+  </si>
+  <si>
+    <t>daysOfMonth,occurrences</t>
+  </si>
+  <si>
+    <t>nth_dom</t>
+  </si>
+  <si>
+    <t>PAT_NTH_FIRST_BIZ_MONTH</t>
+  </si>
+  <si>
+    <t>NTH_FIRST_BIZ_MONTH</t>
+  </si>
+  <si>
+    <t>Nth First Business Day of Month</t>
+  </si>
+  <si>
+    <t>nth_first_biz_month</t>
+  </si>
+  <si>
+    <t>PAT_NTH_LAST_BIZ_MONTH</t>
+  </si>
+  <si>
+    <t>NTH_LAST_BIZ_MONTH</t>
+  </si>
+  <si>
+    <t>Nth Last Business Day of Month</t>
+  </si>
+  <si>
+    <t>nth_last_biz_month</t>
+  </si>
+  <si>
+    <t>PAT_NTH_FIRST_BIZ_QUARTER</t>
+  </si>
+  <si>
+    <t>NTH_FIRST_BIZ_QUARTER</t>
+  </si>
+  <si>
+    <t>Nth First Business Day of Quarter</t>
+  </si>
+  <si>
+    <t>nth_first_biz_quarter</t>
+  </si>
+  <si>
+    <t>PAT_NTH_LAST_BIZ_QUARTER</t>
+  </si>
+  <si>
+    <t>NTH_LAST_BIZ_QUARTER</t>
+  </si>
+  <si>
+    <t>Nth Last Business Day of Quarter</t>
+  </si>
+  <si>
+    <t>nth_last_biz_quarter</t>
+  </si>
+  <si>
+    <t>PAT_FIRST_BIZ_YEAR</t>
+  </si>
+  <si>
+    <t>FIRST_BIZ_YEAR</t>
+  </si>
+  <si>
+    <t>First Business Day of Year</t>
+  </si>
+  <si>
+    <t>date,region</t>
+  </si>
+  <si>
+    <t>first_biz_year</t>
+  </si>
+  <si>
+    <t>PAT_LAST_BIZ_YEAR</t>
+  </si>
+  <si>
+    <t>LAST_BIZ_YEAR</t>
+  </si>
+  <si>
+    <t>Last Business Day of Year</t>
+  </si>
+  <si>
+    <t>last_biz_year</t>
+  </si>
+  <si>
+    <t>PAT_HOLIDAY</t>
+  </si>
+  <si>
+    <t>Holiday</t>
+  </si>
+  <si>
+    <t>holiday</t>
+  </si>
+  <si>
+    <t>runtimeParams</t>
+  </si>
+  <si>
+    <t>configParams</t>
+  </si>
+  <si>
+    <t>dayOfWeek,occurrences</t>
+  </si>
+  <si>
+    <t>Single day-of-week, specific Nth occurrences in a month</t>
+  </si>
+  <si>
+    <t>daysOfWeek,occurrences</t>
+  </si>
+  <si>
+    <t>Multiple days-of-week, specific Nth occurrences in a month</t>
+  </si>
+  <si>
+    <t>Specific calendar day numbers in specific months</t>
+  </si>
+  <si>
+    <t>occurrences</t>
+  </si>
+  <si>
+    <t>First business day of specific months; region excludes holidays</t>
+  </si>
+  <si>
+    <t>Last business day of specific months; region excludes holidays</t>
+  </si>
+  <si>
+    <t>First business day of specific quarters</t>
+  </si>
+  <si>
+    <t>Last business day of specific quarters</t>
+  </si>
+  <si>
+    <t>Single first business day of the calendar year</t>
+  </si>
+  <si>
+    <t>Single last business day of the calendar year</t>
+  </si>
+  <si>
+    <t>IS_HOLIDAY_ON edges queried with region IN [rule.region, 'ALL']</t>
+  </si>
+  <si>
+    <t>ruleId</t>
+  </si>
+  <si>
+    <t>params</t>
+  </si>
+  <si>
+    <t>RULE_1ST_SUNDAY</t>
+  </si>
+  <si>
+    <t>Every 1st Sunday</t>
+  </si>
+  <si>
+    <t>{"dayOfWeek": 7, "occurrences": [1]}</t>
+  </si>
+  <si>
+    <t>1st Sunday of every month. Evaluator receives: date (runtime) + dayOfWeek/occurrences (from params)</t>
+  </si>
+  <si>
+    <t>RULE_WEEKDAY</t>
+  </si>
+  <si>
+    <t>Weekday</t>
+  </si>
+  <si>
+    <t>{"daysOfWeek": [1,2,3,4,5], "occurrences": [1,2,3,4,5]}</t>
+  </si>
+  <si>
+    <t>Any Monday–Friday. Evaluator receives: date (runtime) + daysOfWeek/occurrences (from params)</t>
+  </si>
+  <si>
+    <t>RULE_WEEKEND</t>
+  </si>
+  <si>
+    <t>Weekend</t>
+  </si>
+  <si>
+    <t>{"daysOfWeek": [6,7], "occurrences": [1,2,3,4,5]}</t>
+  </si>
+  <si>
+    <t>Any Saturday or Sunday. Evaluator receives: date (runtime) + daysOfWeek/occurrences (from params)</t>
+  </si>
+  <si>
+    <t>RULE_1ST_2ND_WED</t>
+  </si>
+  <si>
+    <t>Every 1st and 2nd Wednesday</t>
+  </si>
+  <si>
+    <t>{"dayOfWeek": 3, "occurrences": [1,2]}</t>
+  </si>
+  <si>
+    <t>1st and 2nd Wednesday of every month</t>
+  </si>
+  <si>
+    <t>RULE_GLOBAL_HOLIDAYS</t>
+  </si>
+  <si>
+    <t>Global Holidays</t>
+  </si>
+  <si>
+    <t>{}</t>
+  </si>
+  <si>
+    <t>Universal market closures. Evaluator receives: date + region (both runtime); region=ALL</t>
+  </si>
+  <si>
+    <t>RULE_CA_HOLIDAYS</t>
+  </si>
+  <si>
+    <t>Canada Holidays</t>
+  </si>
+  <si>
+    <t>Canadian holidays. Evaluator receives: date + region (both runtime); region=CA</t>
+  </si>
+  <si>
+    <t>RULE_1ST_BD_QUARTER</t>
+  </si>
+  <si>
+    <t>Every 1st BD of Quarter</t>
+  </si>
+  <si>
+    <t>{"occurrences": [1,2,3,4]}</t>
+  </si>
+  <si>
+    <t>First business day of each quarter. Evaluator receives: date + region (runtime) + occurrences (from params)</t>
+  </si>
+  <si>
+    <t>RULE_TUE_TO_FRI</t>
+  </si>
+  <si>
+    <t>Every Tuesday to Friday</t>
+  </si>
+  <si>
+    <t>{"daysOfWeek": [2,3,4,5], "occurrences": [1,2,3,4,5]}</t>
+  </si>
+  <si>
+    <t>Any Tuesday–Friday</t>
+  </si>
+  <si>
+    <t>RULE_1ST_4TH_SUNDAY</t>
+  </si>
+  <si>
+    <t>Every 1st–4th Sunday</t>
+  </si>
+  <si>
+    <t>{"dayOfWeek": 7, "occurrences": [1,2,3,4]}</t>
+  </si>
+  <si>
+    <t>1st through 4th Sunday of every month</t>
+  </si>
+  <si>
+    <t>RULE_US_HOLIDAYS</t>
+  </si>
+  <si>
+    <t>US Holidays</t>
+  </si>
+  <si>
+    <t>US Federal holidays. Evaluator receives: date + region (both runtime); region=US</t>
+  </si>
+  <si>
+    <t>RULE_FIRST_BD_MONTH</t>
+  </si>
+  <si>
+    <t>First Business Day of Month</t>
+  </si>
+  <si>
+    <t>{"occurrences": [1,2,3,4,5,6,7,8,9,10,11,12]}</t>
+  </si>
+  <si>
+    <t>First BD of every month. Evaluator receives: date + region (runtime) + occurrences (from params)</t>
+  </si>
+  <si>
+    <t>RULE_LAST_BD_MONTH</t>
+  </si>
+  <si>
+    <t>Last Business Day of Month</t>
+  </si>
+  <si>
+    <t>Last BD of every month. Evaluator receives: date + region (runtime) + occurrences (from params)</t>
+  </si>
+  <si>
+    <t>PAT_GRAPH_PROPERTY</t>
+  </si>
+  <si>
+    <t>GRAPH_PROPERTY</t>
+  </si>
+  <si>
+    <t>Graph Node Property</t>
+  </si>
+  <si>
+    <t>nodeName,propertyName</t>
+  </si>
+  <si>
+    <t>evaluate_graph_property</t>
+  </si>
+  <si>
+    <t>Reads a boolean property from any calendar hierarchy node (Day/Week/Month/Quarter/Year). Pure Python — computed from the date; no Neo4j lookup needed.</t>
+  </si>
+  <si>
+    <t>RULE_FIRST_OF_MONTH</t>
+  </si>
+  <si>
+    <t>First Day of Month</t>
+  </si>
+  <si>
+    <t>Matches the 1st calendar day of any month. Agent reads Day.isFirstOfMonth directly.</t>
+  </si>
+  <si>
+    <t>RULE_LAST_OF_MONTH</t>
+  </si>
+  <si>
+    <t>Last Day of Month</t>
+  </si>
+  <si>
+    <t>Matches the last calendar day of any month. Agent reads Day.isLastOfMonth directly.</t>
+  </si>
+  <si>
+    <t>RULE_FIRST_OF_QUARTER</t>
+  </si>
+  <si>
+    <t>First Day of Quarter</t>
+  </si>
+  <si>
+    <t>Matches Jan 1, Apr 1, Jul 1, Oct 1. Agent reads Day.isFirstOfQuarter directly.</t>
+  </si>
+  <si>
+    <t>RULE_LAST_OF_QUARTER</t>
+  </si>
+  <si>
+    <t>Last Day of Quarter</t>
+  </si>
+  <si>
+    <t>Matches Mar 31, Jun 30, Sep 30, Dec 31. Agent reads Day.isLastOfQuarter directly.</t>
+  </si>
+  <si>
+    <t>RULE_FIRST_OF_YEAR</t>
+  </si>
+  <si>
+    <t>First Day of Year</t>
+  </si>
+  <si>
+    <t>Matches January 1st. Agent reads Day.isFirstOfYear directly.</t>
+  </si>
+  <si>
+    <t>RULE_LAST_OF_YEAR</t>
+  </si>
+  <si>
+    <t>Last Day of Year</t>
+  </si>
+  <si>
+    <t>Matches December 31st. Agent reads Day.isLastOfYear directly.</t>
+  </si>
+  <si>
+    <t>{"nodeName": "Day", "propertyName": "isFirstOfMonth"}</t>
+  </si>
+  <si>
+    <t>{"nodeName": "Day", "propertyName": "isLastOfMonth"}</t>
+  </si>
+  <si>
+    <t>{"nodeName": "Day", "propertyName": "isFirstOfQuarter"}</t>
+  </si>
+  <si>
+    <t>{"nodeName": "Day", "propertyName": "isLastOfQuarter"}</t>
+  </si>
+  <si>
+    <t>{"nodeName": "Day", "propertyName": "isFirstOfYear"}</t>
+  </si>
+  <si>
+    <t>{"nodeName": "Day", "propertyName": "isLastOfYear"}</t>
+  </si>
+  <si>
+    <t>SKIP</t>
+  </si>
+  <si>
+    <t>RUN_PREVIOUS_BUSINESS_DAY</t>
+  </si>
+  <si>
+    <t>RUN_NEXT_BUSINESS_DAY</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>PAT_NAMED_HOLIDAY</t>
+  </si>
+  <si>
+    <t>NAMED_HOLIDAY</t>
+  </si>
+  <si>
+    <t>named_holiday</t>
+  </si>
+  <si>
+    <t>PAT_SPECIFIC_DATE</t>
+  </si>
+  <si>
+    <t>SPECIFIC_DATE</t>
+  </si>
+  <si>
+    <t>specific_date</t>
+  </si>
+  <si>
+    <t>Named Holidays</t>
+  </si>
+  <si>
+    <t>Specific Calendar Dates</t>
+  </si>
+  <si>
+    <t>holidayNames</t>
+  </si>
+  <si>
+    <t>targetDates</t>
+  </si>
+  <si>
+    <t>Matches any of a list of named holidays in the region. One rule covers multiple holidays — keeps catalog compact.</t>
+  </si>
+  <si>
+    <t>Matches any of a list of hardcoded dates. One rule covers multiple one-off blackouts. Year-specific — review annually.</t>
+  </si>
+  <si>
+    <t>RULE_NewYear_AND_Christmas</t>
+  </si>
+  <si>
+    <t>New Year and Christmas</t>
+  </si>
+  <si>
+    <t>{"holidayNames": ["New Year's Day", "Christmas Day"]}</t>
+  </si>
+  <si>
+    <t>Matches New Year Day and Christmas Day directly</t>
+  </si>
+  <si>
+    <t>RULE_TUE_TO_SAT</t>
+  </si>
+  <si>
+    <t>{"daysOfWeek": [2,3,4,5,6], "occurrences": [1,2,3,4,5]}</t>
+  </si>
+  <si>
+    <t>Any Tuesday–Saturday</t>
+  </si>
+  <si>
+    <t>Every Tuesday to Saturday</t>
+  </si>
+  <si>
+    <t>RULE_4TH_BD_MONTH</t>
+  </si>
+  <si>
+    <t>4th Business Day of Month</t>
+  </si>
+  <si>
+    <t>{"occurrences": [4]}</t>
+  </si>
+  <si>
+    <t>Fourth BD of every month. Evaluator receives: date + region (runtime) + occurrences (from params)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1277,6 +1752,25 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1326,7 +1820,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1348,6 +1842,26 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1674,7 +2188,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -1696,13 +2210,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="B3" t="s">
-        <v>328</v>
+        <v>269</v>
       </c>
       <c r="C3" t="s">
-        <v>329</v>
+        <v>270</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -1716,13 +2230,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
       <c r="B4" t="s">
-        <v>347</v>
+        <v>288</v>
       </c>
       <c r="C4" t="s">
-        <v>347</v>
+        <v>288</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -1731,18 +2245,18 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>384</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>321</v>
+        <v>264</v>
       </c>
       <c r="B5" t="s">
-        <v>358</v>
+        <v>299</v>
       </c>
       <c r="C5" t="s">
-        <v>359</v>
+        <v>300</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -1751,18 +2265,18 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>384</v>
+        <v>325</v>
       </c>
       <c r="B6" t="s">
-        <v>385</v>
+        <v>326</v>
       </c>
       <c r="C6" t="s">
-        <v>385</v>
+        <v>326</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -1777,6 +2291,853 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E11C9B5E-0362-415A-85F1-29574F98361F}">
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.26953125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="19.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="35.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="H2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D3" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="H3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" t="s">
+        <v>187</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F4" t="s">
+        <v>183</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H4" t="s">
+        <v>186</v>
+      </c>
+      <c r="I4" t="s">
+        <v>191</v>
+      </c>
+      <c r="J4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F5" t="s">
+        <v>249</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="H5" t="s">
+        <v>186</v>
+      </c>
+      <c r="I5" t="s">
+        <v>193</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F6" t="s">
+        <v>183</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="H6" t="s">
+        <v>198</v>
+      </c>
+      <c r="J6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>247</v>
+      </c>
+      <c r="B7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H7" t="s">
+        <v>198</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" t="s">
+        <v>228</v>
+      </c>
+      <c r="E8" t="s">
+        <v>184</v>
+      </c>
+      <c r="F8" t="s">
+        <v>249</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H8" t="s">
+        <v>199</v>
+      </c>
+      <c r="I8" t="s">
+        <v>241</v>
+      </c>
+      <c r="J8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05669172-4566-411C-BAD9-C6B812325413}">
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>459</v>
+      </c>
+      <c r="B3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>490</v>
+      </c>
+      <c r="B4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>509</v>
+      </c>
+      <c r="B5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>506</v>
+      </c>
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5</v>
+      </c>
+      <c r="E6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>490</v>
+      </c>
+      <c r="B7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" t="s">
+        <v>268</v>
+      </c>
+      <c r="E7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>490</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D8" t="s">
+        <v>287</v>
+      </c>
+      <c r="E8" t="s">
+        <v>103</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>459</v>
+      </c>
+      <c r="B9" t="s">
+        <v>101</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
+        <v>268</v>
+      </c>
+      <c r="E9" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>459</v>
+      </c>
+      <c r="B10" t="s">
+        <v>101</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" t="s">
+        <v>287</v>
+      </c>
+      <c r="E10" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B2" s="10">
+        <v>46023</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" s="10">
+        <v>46115</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B4" s="10">
+        <v>46118</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B5" s="10">
+        <v>46381</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B6" s="10">
+        <v>46382</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>372</v>
+      </c>
+      <c r="B7" s="10">
+        <v>46041</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>374</v>
+      </c>
+      <c r="B8" s="10">
+        <v>46069</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B9" s="10">
+        <v>46167</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>345</v>
+      </c>
+      <c r="B10" s="10">
+        <v>46192</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D10" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>348</v>
+      </c>
+      <c r="B11" s="10">
+        <v>46206</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D11" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>350</v>
+      </c>
+      <c r="B12" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D12" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>352</v>
+      </c>
+      <c r="B13" s="10">
+        <v>46307</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D13" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>354</v>
+      </c>
+      <c r="B14" s="10">
+        <v>46337</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D14" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>356</v>
+      </c>
+      <c r="B15" s="10">
+        <v>46352</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D15" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>358</v>
+      </c>
+      <c r="B16" s="10">
+        <v>46069</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D16" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>378</v>
+      </c>
+      <c r="B17" s="10">
+        <v>46160</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D17" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>380</v>
+      </c>
+      <c r="B18" s="10">
+        <v>46204</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D18" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>382</v>
+      </c>
+      <c r="B19" s="10">
+        <v>46237</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D19" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>384</v>
+      </c>
+      <c r="B20" s="10">
+        <v>46272</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D20" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>386</v>
+      </c>
+      <c r="B21" s="10">
+        <v>46295</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D21" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>388</v>
+      </c>
+      <c r="B22" s="10">
+        <v>46307</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D22" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>389</v>
+      </c>
+      <c r="B23" s="10">
+        <v>46337</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D23" t="s">
+        <v>390</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2457C5B2-79A5-4ABF-A9FF-0D9D109676D8}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -1796,7 +3157,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>213</v>
+        <v>157</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -1807,376 +3168,376 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>272</v>
+        <v>216</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="C2" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>266</v>
+        <v>210</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>273</v>
+        <v>217</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>211</v>
       </c>
       <c r="C3" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>267</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>274</v>
+        <v>218</v>
       </c>
       <c r="B4" t="s">
-        <v>268</v>
+        <v>212</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>268</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>275</v>
+        <v>219</v>
       </c>
       <c r="B5" t="s">
-        <v>269</v>
+        <v>213</v>
       </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>269</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>276</v>
+        <v>220</v>
       </c>
       <c r="B6" t="s">
-        <v>270</v>
+        <v>214</v>
       </c>
       <c r="C6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
         <v>214</v>
-      </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>288</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>290</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>307</v>
+        <v>250</v>
       </c>
       <c r="B8" t="s">
-        <v>314</v>
+        <v>257</v>
       </c>
       <c r="C8" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>314</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>308</v>
+        <v>251</v>
       </c>
       <c r="B9" t="s">
-        <v>315</v>
+        <v>258</v>
       </c>
       <c r="C9" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>315</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>309</v>
+        <v>252</v>
       </c>
       <c r="B10" t="s">
-        <v>316</v>
+        <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>316</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>310</v>
+        <v>253</v>
       </c>
       <c r="B11" t="s">
-        <v>317</v>
+        <v>260</v>
       </c>
       <c r="C11" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>317</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>311</v>
+        <v>254</v>
       </c>
       <c r="B12" t="s">
-        <v>318</v>
+        <v>261</v>
       </c>
       <c r="C12" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>318</v>
+        <v>261</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>312</v>
+        <v>255</v>
       </c>
       <c r="B13" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
       <c r="C13" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>319</v>
+        <v>262</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>313</v>
+        <v>256</v>
       </c>
       <c r="B14" t="s">
-        <v>320</v>
+        <v>263</v>
       </c>
       <c r="C14" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>320</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>274</v>
       </c>
       <c r="B15" t="s">
-        <v>334</v>
+        <v>275</v>
       </c>
       <c r="C15" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>334</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>376</v>
+        <v>317</v>
       </c>
       <c r="B16" t="s">
-        <v>368</v>
+        <v>309</v>
       </c>
       <c r="C16" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>361</v>
+        <v>302</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>377</v>
+        <v>318</v>
       </c>
       <c r="B17" t="s">
-        <v>369</v>
+        <v>310</v>
       </c>
       <c r="C17" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>362</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>378</v>
+        <v>319</v>
       </c>
       <c r="B18" t="s">
-        <v>370</v>
+        <v>311</v>
       </c>
       <c r="C18" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>363</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>379</v>
+        <v>320</v>
       </c>
       <c r="B19" t="s">
-        <v>371</v>
+        <v>312</v>
       </c>
       <c r="C19" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>360</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>380</v>
+        <v>321</v>
       </c>
       <c r="B20" t="s">
-        <v>372</v>
+        <v>313</v>
       </c>
       <c r="C20" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>364</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>381</v>
+        <v>322</v>
       </c>
       <c r="B21" t="s">
-        <v>373</v>
+        <v>314</v>
       </c>
       <c r="C21" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>365</v>
+        <v>306</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>382</v>
+        <v>323</v>
       </c>
       <c r="B22" t="s">
-        <v>374</v>
+        <v>315</v>
       </c>
       <c r="C22" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>366</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>383</v>
+        <v>324</v>
       </c>
       <c r="B23" t="s">
-        <v>375</v>
+        <v>316</v>
       </c>
       <c r="C23" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>367</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -2184,7 +3545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B10723-7323-494A-8BD9-19954F3DA961}">
   <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2204,170 +3565,170 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>230</v>
+        <v>174</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>234</v>
+        <v>178</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>235</v>
+        <v>179</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>111</v>
       </c>
       <c r="D2" t="s">
-        <v>210</v>
+        <v>154</v>
       </c>
       <c r="E2" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="F2" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="G2" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="H2" t="s">
-        <v>241</v>
+        <v>185</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>250</v>
+        <v>194</v>
       </c>
       <c r="J2" t="s">
-        <v>242</v>
+        <v>186</v>
       </c>
       <c r="K2" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" t="s">
         <v>183</v>
       </c>
-      <c r="D3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E3" t="s">
-        <v>239</v>
-      </c>
       <c r="G3" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="H3" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
       <c r="J3" t="s">
-        <v>242</v>
+        <v>186</v>
       </c>
       <c r="K3" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="E4" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="F4" t="s">
-        <v>219</v>
+        <v>163</v>
       </c>
       <c r="G4" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="H4" t="s">
-        <v>241</v>
+        <v>185</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>252</v>
+        <v>196</v>
       </c>
       <c r="J4" t="s">
-        <v>242</v>
+        <v>186</v>
       </c>
       <c r="K4" t="s">
-        <v>249</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="D5" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="E5" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="F5" t="s">
-        <v>217</v>
+        <v>161</v>
       </c>
       <c r="G5" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="H5" t="s">
-        <v>241</v>
+        <v>185</v>
       </c>
       <c r="J5" t="s">
-        <v>254</v>
+        <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="J6" t="s">
-        <v>255</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
@@ -2375,380 +3736,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05669172-4566-411C-BAD9-C6B812325413}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.26953125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" t="s">
-        <v>133</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>156</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>156</v>
-      </c>
-      <c r="F5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>156</v>
-      </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>327</v>
-      </c>
-      <c r="E7" t="s">
-        <v>156</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>136</v>
-      </c>
-      <c r="B8" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" t="s">
-        <v>346</v>
-      </c>
-      <c r="E8" t="s">
-        <v>156</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>137</v>
-      </c>
-      <c r="B9" t="s">
-        <v>139</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D9" t="s">
-        <v>327</v>
-      </c>
-      <c r="E9" t="s">
-        <v>133</v>
-      </c>
-      <c r="F9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>137</v>
-      </c>
-      <c r="B10" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>346</v>
-      </c>
-      <c r="E10" t="s">
-        <v>133</v>
-      </c>
-      <c r="F10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.26953125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>101</v>
-      </c>
-      <c r="B5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C5" t="s">
-        <v>103</v>
-      </c>
-      <c r="D5" t="s">
-        <v>136</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D6" t="s">
-        <v>136</v>
-      </c>
-      <c r="E6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>107</v>
-      </c>
-      <c r="B7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D7" t="s">
-        <v>136</v>
-      </c>
-      <c r="E7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" t="s">
-        <v>112</v>
-      </c>
-      <c r="D8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45.81640625" bestFit="1" customWidth="1"/>
@@ -2757,7 +3747,7 @@
     <col min="5" max="5" width="8.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2774,10 +3764,10 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -2793,11 +3783,8 @@
       <c r="E2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -2813,11 +3800,8 @@
       <c r="E3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -2833,11 +3817,8 @@
       <c r="E4" t="b">
         <v>1</v>
       </c>
-      <c r="G4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -2853,11 +3834,8 @@
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -2873,11 +3851,8 @@
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="G6" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2893,11 +3868,8 @@
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="G7" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -2913,11 +3885,8 @@
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="G8" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -2933,19 +3902,16 @@
       <c r="E9" t="b">
         <v>1</v>
       </c>
-      <c r="G9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>386</v>
+        <v>327</v>
       </c>
       <c r="B10" t="s">
-        <v>386</v>
+        <v>327</v>
       </c>
       <c r="C10" t="s">
-        <v>387</v>
+        <v>328</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -2954,15 +3920,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>388</v>
+        <v>329</v>
       </c>
       <c r="B11" t="s">
-        <v>388</v>
+        <v>329</v>
       </c>
       <c r="C11" t="s">
-        <v>389</v>
+        <v>330</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -2971,15 +3937,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>390</v>
+        <v>331</v>
       </c>
       <c r="B12" t="s">
-        <v>390</v>
+        <v>331</v>
       </c>
       <c r="C12" t="s">
-        <v>391</v>
+        <v>332</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -2988,15 +3954,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>392</v>
+        <v>333</v>
       </c>
       <c r="B13" t="s">
-        <v>392</v>
+        <v>333</v>
       </c>
       <c r="C13" t="s">
-        <v>393</v>
+        <v>334</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -3014,7 +3980,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44296FCF-98A5-4DD9-A7AF-D431FBFB26B8}">
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="45.81640625" bestFit="1" customWidth="1"/>
@@ -3023,7 +3989,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>298</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
@@ -3098,7 +4064,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -3106,7 +4072,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -3114,7 +4080,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -3122,7 +4088,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -3130,7 +4096,7 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -3138,7 +4104,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -3146,7 +4112,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -3154,7 +4120,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
@@ -3162,7 +4128,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
@@ -3170,7 +4136,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
@@ -3178,7 +4144,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
@@ -3186,7 +4152,7 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
@@ -3194,39 +4160,47 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>386</v>
+        <v>327</v>
       </c>
       <c r="B23" t="s">
-        <v>384</v>
+        <v>325</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>388</v>
+        <v>329</v>
       </c>
       <c r="B24" t="s">
-        <v>384</v>
+        <v>325</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>390</v>
+        <v>331</v>
       </c>
       <c r="B25" t="s">
-        <v>384</v>
+        <v>325</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>392</v>
+        <v>333</v>
       </c>
       <c r="B26" t="s">
-        <v>384</v>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>342</v>
+      </c>
+      <c r="B27" t="s">
+        <v>325</v>
       </c>
     </row>
   </sheetData>
@@ -3261,10 +4235,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>216</v>
+        <v>160</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>20</v>
@@ -3273,7 +4247,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>271</v>
+        <v>215</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>2</v>
@@ -3281,10 +4255,10 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>110</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>166</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
@@ -3299,15 +4273,15 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>277</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>164</v>
+        <v>111</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
@@ -3322,15 +4296,15 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>278</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
@@ -3345,15 +4319,15 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>279</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>186</v>
+        <v>133</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
@@ -3368,15 +4342,15 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>280</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>212</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -3391,15 +4365,15 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>281</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>118</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>331</v>
+        <v>272</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
@@ -3414,12 +4388,12 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>332</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>172</v>
+        <v>119</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>29</v>
@@ -3437,12 +4411,12 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>120</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -3460,12 +4434,12 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>174</v>
+        <v>121</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>33</v>
@@ -3483,12 +4457,12 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>35</v>
@@ -3506,12 +4480,12 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>37</v>
@@ -3529,12 +4503,12 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>177</v>
+        <v>124</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -3552,12 +4526,12 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>125</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>41</v>
@@ -3575,12 +4549,12 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>43</v>
@@ -3598,12 +4572,12 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>127</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>45</v>
@@ -3621,187 +4595,187 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>128</v>
       </c>
       <c r="B17" t="s">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="C17" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="E17" t="s">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>291</v>
+        <v>344</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>182</v>
+        <v>129</v>
       </c>
       <c r="B18" t="s">
-        <v>220</v>
+        <v>164</v>
       </c>
       <c r="C18" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="E18" t="s">
-        <v>220</v>
+        <v>164</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>292</v>
+        <v>235</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="B19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C19" t="s">
+        <v>230</v>
+      </c>
+      <c r="E19" t="s">
+        <v>166</v>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
         <v>222</v>
-      </c>
-      <c r="C19" t="s">
-        <v>286</v>
-      </c>
-      <c r="E19" t="s">
-        <v>222</v>
-      </c>
-      <c r="G19" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="B20" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="C20" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="E20" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>293</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>185</v>
+        <v>132</v>
       </c>
       <c r="B21" t="s">
-        <v>224</v>
+        <v>168</v>
       </c>
       <c r="C21" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="E21" t="s">
-        <v>224</v>
+        <v>168</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>294</v>
+        <v>237</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>283</v>
+        <v>227</v>
       </c>
       <c r="B22" t="s">
-        <v>225</v>
+        <v>169</v>
       </c>
       <c r="C22" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="E22" t="s">
-        <v>225</v>
+        <v>169</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>295</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>284</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s">
-        <v>226</v>
+        <v>170</v>
       </c>
       <c r="C23" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="E23" t="s">
-        <v>226</v>
+        <v>170</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>296</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>285</v>
+        <v>229</v>
       </c>
       <c r="B24" t="s">
-        <v>227</v>
+        <v>171</v>
       </c>
       <c r="C24" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="E24" t="s">
-        <v>227</v>
+        <v>171</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>297</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>399</v>
+        <v>340</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>400</v>
+        <v>341</v>
       </c>
       <c r="C25" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="E25" t="s">
-        <v>400</v>
+        <v>341</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>293</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -3812,18 +4786,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4D3A986-0BD4-4414-9DF3-09CE83567AC3}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.1796875" style="3"/>
     <col min="2" max="2" width="45.81640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="9.1796875" style="3"/>
-    <col min="7" max="7" width="23.1796875" style="3" customWidth="1"/>
-    <col min="8" max="16384" width="9.1796875" style="3"/>
+    <col min="4" max="16384" width="9.1796875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3834,24 +4806,18 @@
         <v>9</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>17</v>
@@ -3859,16 +4825,10 @@
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G2">
-        <v>260000</v>
-      </c>
-      <c r="H2">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
@@ -3877,21 +4837,15 @@
         <v>5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G3">
-        <v>370000</v>
-      </c>
-      <c r="H3">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>13</v>
@@ -3900,21 +4854,15 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G4">
-        <v>420000</v>
-      </c>
-      <c r="H4">
-        <v>420000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>14</v>
@@ -3923,21 +4871,15 @@
         <v>5</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G5">
-        <v>400000</v>
-      </c>
-      <c r="H5">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>16</v>
@@ -3946,21 +4888,15 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G6">
-        <v>670000</v>
-      </c>
-      <c r="H6">
-        <v>540000</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
@@ -3969,21 +4905,15 @@
         <v>5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G7">
-        <v>360000</v>
-      </c>
-      <c r="H7">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>127</v>
+        <v>89</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>15</v>
@@ -3992,21 +4922,15 @@
         <v>5</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G8">
-        <v>380000</v>
-      </c>
-      <c r="H8">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>11</v>
@@ -4015,24 +4939,18 @@
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>192</v>
+        <v>139</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G9">
-        <v>280000</v>
-      </c>
-      <c r="H9">
-        <v>360000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>18</v>
@@ -4041,450 +4959,347 @@
         <v>5</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G10">
-        <v>420000</v>
-      </c>
-      <c r="H10">
-        <v>360000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>335</v>
+        <v>276</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>327</v>
-      </c>
-      <c r="G11">
-        <v>250000</v>
-      </c>
-      <c r="H11">
-        <v>240000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>336</v>
+        <v>277</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>339</v>
+        <v>280</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G12">
-        <v>380000</v>
-      </c>
-      <c r="H12">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>337</v>
+        <v>278</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>340</v>
+        <v>281</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G13">
-        <v>410000</v>
-      </c>
-      <c r="H13">
-        <v>420000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>339</v>
+        <v>280</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>342</v>
+        <v>283</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G14">
-        <v>450000</v>
-      </c>
-      <c r="H14">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>340</v>
+        <v>281</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>341</v>
+        <v>282</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G15">
-        <v>590000</v>
-      </c>
-      <c r="H15">
-        <v>540000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>341</v>
+        <v>282</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>344</v>
+        <v>285</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G16">
-        <v>350000</v>
-      </c>
-      <c r="H16">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>342</v>
+        <v>283</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>335</v>
+        <v>276</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G17">
-        <v>360000</v>
-      </c>
-      <c r="H17">
-        <v>300000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>343</v>
+        <v>284</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>338</v>
+        <v>279</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G18">
-        <v>320000</v>
-      </c>
-      <c r="H18">
-        <v>360000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>344</v>
+        <v>285</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>335</v>
+        <v>276</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G19">
-        <v>390000</v>
-      </c>
-      <c r="H19">
-        <v>360000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>348</v>
+        <v>289</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>350</v>
+        <v>291</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G20">
-        <v>20000</v>
-      </c>
-      <c r="H20">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>349</v>
+        <v>290</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>351</v>
+        <v>292</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G21">
-        <v>15000</v>
-      </c>
-      <c r="H21">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>350</v>
+        <v>291</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>352</v>
+        <v>293</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G22">
-        <v>25000</v>
-      </c>
-      <c r="H22">
-        <v>15000</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>351</v>
+        <v>292</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>352</v>
+        <v>293</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G23">
-        <v>10000</v>
-      </c>
-      <c r="H23">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>352</v>
+        <v>293</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G24">
-        <v>5000</v>
-      </c>
-      <c r="H24">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>353</v>
+        <v>294</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G25">
-        <v>10000</v>
-      </c>
-      <c r="H25">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="B26" t="s">
-        <v>386</v>
+        <v>335</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>342</v>
       </c>
       <c r="C26" t="s">
-        <v>384</v>
+        <v>325</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>396</v>
+        <v>336</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G26" s="3">
-        <v>12000</v>
-      </c>
-      <c r="H26" s="3">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>395</v>
+        <v>336</v>
       </c>
       <c r="B27" t="s">
-        <v>388</v>
+        <v>327</v>
       </c>
       <c r="C27" t="s">
-        <v>384</v>
+        <v>325</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>397</v>
+        <v>337</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G27" s="3">
-        <v>8000</v>
-      </c>
-      <c r="H27" s="3">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>396</v>
+        <v>337</v>
       </c>
       <c r="B28" t="s">
-        <v>390</v>
+        <v>329</v>
       </c>
       <c r="C28" t="s">
-        <v>384</v>
+        <v>325</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>395</v>
+        <v>338</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G28" s="3">
-        <v>5000</v>
-      </c>
-      <c r="H28" s="3">
-        <v>7000</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>397</v>
+        <v>338</v>
       </c>
       <c r="B29" t="s">
-        <v>392</v>
+        <v>331</v>
       </c>
       <c r="C29" t="s">
-        <v>384</v>
+        <v>325</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>343</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G29" s="3">
-        <v>20000</v>
-      </c>
-      <c r="H29" s="3">
-        <v>25000</v>
+        <v>141</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A30" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B30" t="s">
+        <v>333</v>
+      </c>
+      <c r="C30" t="s">
+        <v>325</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -4515,50 +5330,50 @@
         <v>46</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>187</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>160</v>
+        <v>107</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>163</v>
+        <v>110</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="F2" s="3" t="b">
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>164</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -4567,44 +5382,44 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>159</v>
+        <v>106</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>196</v>
+        <v>143</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>162</v>
+        <v>109</v>
       </c>
       <c r="D4" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="F4" s="3" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>190</v>
+        <v>137</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>191</v>
+        <v>138</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>169</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -4613,53 +5428,53 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>189</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>330</v>
+        <v>271</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>171</v>
+        <v>118</v>
       </c>
       <c r="E6" t="s">
-        <v>327</v>
+        <v>268</v>
       </c>
       <c r="F6" s="3" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>158</v>
+        <v>105</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>170</v>
+        <v>117</v>
       </c>
       <c r="E7" t="s">
-        <v>346</v>
+        <v>287</v>
       </c>
       <c r="F7" s="3" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>188</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -4670,575 +5485,520 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:M18"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="40.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.7265625" style="3" customWidth="1"/>
-    <col min="13" max="13" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="34.7265625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="8.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>56</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>57</v>
-      </c>
       <c r="B2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2">
+        <v>360000</v>
+      </c>
+      <c r="H2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I2" t="s">
         <v>70</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G2">
-        <v>360000</v>
-      </c>
-      <c r="I2" t="s">
-        <v>198</v>
       </c>
       <c r="J2" t="s">
         <v>71</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G3">
+      <c r="F3">
         <v>300000</v>
       </c>
+      <c r="H3" t="s">
+        <v>145</v>
+      </c>
       <c r="I3" t="s">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="J3" t="s">
         <v>71</v>
       </c>
-      <c r="K3" t="s">
-        <v>72</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="L3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G4">
+        <v>73</v>
+      </c>
+      <c r="F4">
         <v>420000</v>
       </c>
+      <c r="H4" t="s">
+        <v>145</v>
+      </c>
       <c r="I4" t="s">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="J4" t="s">
         <v>71</v>
       </c>
-      <c r="K4" t="s">
-        <v>72</v>
-      </c>
-      <c r="L4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="M4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>202</v>
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>112</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
-      </c>
-      <c r="F5" t="s">
-        <v>210</v>
-      </c>
-      <c r="G5">
+        <v>154</v>
+      </c>
+      <c r="F5">
         <v>600000</v>
       </c>
+      <c r="H5" t="s">
+        <v>145</v>
+      </c>
       <c r="I5" t="s">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="J5" t="s">
         <v>71</v>
       </c>
-      <c r="K5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="M5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="L5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G6">
+        <v>75</v>
+      </c>
+      <c r="F6">
         <v>300000</v>
       </c>
+      <c r="H6" t="s">
+        <v>145</v>
+      </c>
       <c r="I6" t="s">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="J6" t="s">
         <v>71</v>
       </c>
-      <c r="K6" t="s">
-        <v>72</v>
-      </c>
-      <c r="L6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="L6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G7">
+        <v>76</v>
+      </c>
+      <c r="F7">
         <v>540000</v>
       </c>
+      <c r="H7" t="s">
+        <v>145</v>
+      </c>
       <c r="I7" t="s">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="J7" t="s">
         <v>71</v>
       </c>
-      <c r="K7" t="s">
-        <v>72</v>
-      </c>
-      <c r="L7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="L7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G8">
+        <v>77</v>
+      </c>
+      <c r="F8">
         <v>240000</v>
       </c>
+      <c r="H8" t="s">
+        <v>145</v>
+      </c>
       <c r="I8" t="s">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s">
         <v>71</v>
       </c>
-      <c r="K8" t="s">
-        <v>72</v>
-      </c>
-      <c r="L8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="L8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G9">
+        <v>78</v>
+      </c>
+      <c r="F9">
         <v>360000</v>
       </c>
+      <c r="H9" t="s">
+        <v>145</v>
+      </c>
       <c r="I9" t="s">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="J9" t="s">
         <v>71</v>
       </c>
-      <c r="K9" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="L9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10">
+        <v>3600000</v>
+      </c>
+      <c r="H10" t="s">
+        <v>145</v>
+      </c>
+      <c r="I10" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
         <v>65</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" t="s">
+        <v>146</v>
+      </c>
+      <c r="I11" t="s">
+        <v>8</v>
+      </c>
+      <c r="J11" t="s">
+        <v>154</v>
+      </c>
+      <c r="K11" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12" t="s">
+        <v>146</v>
+      </c>
+      <c r="I12" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" t="s">
+        <v>154</v>
+      </c>
+      <c r="K12" t="s">
+        <v>111</v>
+      </c>
+      <c r="L12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="G13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" t="s">
+        <v>146</v>
+      </c>
+      <c r="I13" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" t="s">
+        <v>154</v>
+      </c>
+      <c r="K13" t="s">
+        <v>112</v>
+      </c>
+      <c r="L13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" t="s">
+        <v>154</v>
+      </c>
+      <c r="K14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>266</v>
+      </c>
+      <c r="B15" t="s">
+        <v>265</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.29236111111111113</v>
+      </c>
+      <c r="G15" t="s">
+        <v>47</v>
+      </c>
+      <c r="H15" t="s">
+        <v>146</v>
+      </c>
+      <c r="I15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" t="s">
         <v>80</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G10">
-        <v>3600000</v>
-      </c>
-      <c r="I10" t="s">
-        <v>198</v>
-      </c>
-      <c r="J10" t="s">
-        <v>71</v>
-      </c>
-      <c r="K10" t="s">
-        <v>82</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="M10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H11" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" t="s">
-        <v>199</v>
-      </c>
-      <c r="J11" t="s">
-        <v>8</v>
-      </c>
-      <c r="K11" t="s">
-        <v>210</v>
-      </c>
-      <c r="L11" t="s">
-        <v>163</v>
-      </c>
-      <c r="M11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H12" t="s">
-        <v>47</v>
-      </c>
-      <c r="I12" t="s">
-        <v>199</v>
-      </c>
-      <c r="J12" t="s">
-        <v>8</v>
-      </c>
-      <c r="K12" t="s">
-        <v>210</v>
-      </c>
-      <c r="L12" t="s">
-        <v>164</v>
-      </c>
-      <c r="M12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="H13" t="s">
-        <v>47</v>
-      </c>
-      <c r="I13" t="s">
-        <v>199</v>
-      </c>
-      <c r="J13" t="s">
-        <v>8</v>
-      </c>
-      <c r="K13" t="s">
-        <v>210</v>
-      </c>
-      <c r="L13" t="s">
-        <v>165</v>
-      </c>
-      <c r="M13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="29" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>200</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H14" t="s">
-        <v>47</v>
-      </c>
-      <c r="I14" t="s">
-        <v>199</v>
-      </c>
-      <c r="J14" t="s">
-        <v>8</v>
-      </c>
-      <c r="K14" t="s">
-        <v>210</v>
-      </c>
-      <c r="L14" t="s">
-        <v>169</v>
-      </c>
-      <c r="M14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>323</v>
-      </c>
-      <c r="B15" t="s">
-        <v>322</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D15" s="8">
-        <v>0.29236111111111113</v>
-      </c>
-      <c r="H15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I15" t="s">
-        <v>199</v>
-      </c>
-      <c r="J15" t="s">
-        <v>8</v>
-      </c>
-      <c r="K15" t="s">
-        <v>82</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="M15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+      <c r="K15" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="L15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>345</v>
+        <v>286</v>
       </c>
       <c r="B16" t="s">
-        <v>326</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G16">
+        <v>267</v>
+      </c>
+      <c r="F16">
         <v>3200000</v>
       </c>
+      <c r="H16" t="s">
+        <v>145</v>
+      </c>
       <c r="I16" t="s">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="J16" t="s">
-        <v>71</v>
-      </c>
-      <c r="K16" t="s">
-        <v>82</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="M16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="L16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>355</v>
+        <v>296</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G17">
+        <v>297</v>
+      </c>
+      <c r="F17">
         <v>60000</v>
       </c>
+      <c r="H17" t="s">
+        <v>145</v>
+      </c>
       <c r="I17" t="s">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="J17" t="s">
-        <v>71</v>
-      </c>
-      <c r="K17" t="s">
-        <v>82</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="M17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="29" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="L17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>355</v>
+        <v>296</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G18">
+        <v>339</v>
+      </c>
+      <c r="F18">
         <v>60000</v>
       </c>
+      <c r="H18" t="s">
+        <v>145</v>
+      </c>
       <c r="I18" t="s">
-        <v>198</v>
+        <v>70</v>
       </c>
       <c r="J18" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="K18" t="s">
-        <v>82</v>
-      </c>
-      <c r="L18" t="s">
-        <v>384</v>
-      </c>
-      <c r="M18" t="b">
+        <v>325</v>
+      </c>
+      <c r="L18" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5250,163 +6010,410 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultColWidth="15.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="29.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="6" width="15.36328125" style="15"/>
+    <col min="7" max="7" width="40.453125" style="15" customWidth="1"/>
+    <col min="8" max="8" width="7.1796875" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.90625" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="15.36328125" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>438</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>439</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>394</v>
+      </c>
+      <c r="G1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>138</v>
-      </c>
-      <c r="B2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="I2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="I3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C4" t="s">
-        <v>90</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" t="s">
-        <v>146</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="I5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="29" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" t="s">
-        <v>146</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="I6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B7" t="s">
-        <v>151</v>
-      </c>
-      <c r="C7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="I7" t="b">
+      <c r="H1" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>399</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="H2" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>401</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>403</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="H3" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>408</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="H4" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>412</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="H5" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>414</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>416</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="H6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="F7" s="15" t="s">
+        <v>421</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="H7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>423</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>449</v>
+      </c>
+      <c r="H8" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>427</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>450</v>
+      </c>
+      <c r="H9" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
+        <v>431</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>433</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="G10" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="H10" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="H11" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="52" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>504</v>
+      </c>
+      <c r="G12" s="15" t="s">
+        <v>505</v>
+      </c>
+      <c r="H12" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="48" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>542</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>536</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="H13" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="48" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="H14" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="15">
         <v>1</v>
       </c>
     </row>
@@ -5416,272 +6423,475 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E11C9B5E-0362-415A-85F1-29574F98361F}">
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A341CB3-E044-445E-8816-E6B6E23CAA09}">
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="26.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="34.26953125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="19.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="35.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="27.54296875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="41.90625" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G1" s="6" t="s">
+    <row r="1" spans="1:7" s="13" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="G1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>455</v>
       </c>
       <c r="B2" t="s">
-        <v>238</v>
+        <v>456</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>239</v>
+        <v>398</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="H2" t="s">
-        <v>242</v>
-      </c>
-      <c r="I2" t="s">
-        <v>243</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>300</v>
+        <v>459</v>
       </c>
       <c r="B3" t="s">
-        <v>238</v>
+        <v>460</v>
       </c>
       <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F3" t="s">
-        <v>306</v>
+        <v>402</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="H3" t="s">
-        <v>242</v>
-      </c>
-      <c r="I3" t="s">
-        <v>243</v>
-      </c>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>301</v>
+        <v>463</v>
       </c>
       <c r="B4" t="s">
-        <v>244</v>
+        <v>464</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D4" t="s">
-        <v>183</v>
-      </c>
-      <c r="E4" t="s">
-        <v>240</v>
-      </c>
-      <c r="F4" t="s">
-        <v>239</v>
+        <v>402</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="H4" t="s">
-        <v>242</v>
-      </c>
-      <c r="I4" t="s">
-        <v>247</v>
-      </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>302</v>
+        <v>467</v>
       </c>
       <c r="B5" t="s">
-        <v>248</v>
+        <v>468</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" t="s">
-        <v>182</v>
-      </c>
-      <c r="E5" t="s">
-        <v>240</v>
-      </c>
-      <c r="F5" t="s">
-        <v>306</v>
+        <v>398</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="H5" t="s">
-        <v>242</v>
-      </c>
-      <c r="I5" t="s">
-        <v>249</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>303</v>
+        <v>471</v>
       </c>
       <c r="B6" t="s">
-        <v>253</v>
+        <v>472</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>182</v>
-      </c>
-      <c r="E6" t="s">
-        <v>240</v>
-      </c>
-      <c r="F6" t="s">
-        <v>239</v>
+        <v>362</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="H6" t="s">
-        <v>254</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>304</v>
+        <v>475</v>
       </c>
       <c r="B7" t="s">
-        <v>253</v>
+        <v>476</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="D7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E7" t="s">
-        <v>240</v>
-      </c>
-      <c r="F7" t="s">
-        <v>306</v>
+        <v>359</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="H7" t="s">
-        <v>254</v>
-      </c>
-      <c r="J7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>305</v>
+        <v>478</v>
       </c>
       <c r="B8" t="s">
-        <v>261</v>
+        <v>479</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" t="s">
-        <v>284</v>
-      </c>
-      <c r="E8" t="s">
-        <v>240</v>
-      </c>
-      <c r="F8" t="s">
-        <v>306</v>
+        <v>419</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H8" t="s">
-        <v>255</v>
-      </c>
-      <c r="I8" t="s">
-        <v>298</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>482</v>
+      </c>
+      <c r="B9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C9" t="s">
+        <v>402</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>486</v>
+      </c>
+      <c r="B10" t="s">
+        <v>487</v>
+      </c>
+      <c r="C10" t="s">
+        <v>398</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>490</v>
+      </c>
+      <c r="B11" t="s">
+        <v>491</v>
+      </c>
+      <c r="C11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D11" t="s">
+        <v>346</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>493</v>
+      </c>
+      <c r="B12" t="s">
+        <v>494</v>
+      </c>
+      <c r="C12" t="s">
+        <v>411</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>497</v>
+      </c>
+      <c r="B13" t="s">
+        <v>498</v>
+      </c>
+      <c r="C13" t="s">
+        <v>415</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>506</v>
+      </c>
+      <c r="B14" t="s">
+        <v>507</v>
+      </c>
+      <c r="C14" t="s">
+        <v>501</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>509</v>
+      </c>
+      <c r="B15" t="s">
+        <v>510</v>
+      </c>
+      <c r="C15" t="s">
+        <v>501</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>512</v>
+      </c>
+      <c r="B16" t="s">
+        <v>513</v>
+      </c>
+      <c r="C16" t="s">
+        <v>501</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>515</v>
+      </c>
+      <c r="B17" t="s">
+        <v>516</v>
+      </c>
+      <c r="C17" t="s">
+        <v>501</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>518</v>
+      </c>
+      <c r="B18" t="s">
+        <v>519</v>
+      </c>
+      <c r="C18" t="s">
+        <v>501</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>521</v>
+      </c>
+      <c r="B19" t="s">
+        <v>522</v>
+      </c>
+      <c r="C19" t="s">
+        <v>501</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>546</v>
+      </c>
+      <c r="B20" t="s">
+        <v>547</v>
+      </c>
+      <c r="C20" t="s">
+        <v>535</v>
+      </c>
+      <c r="D20" t="s">
+        <v>362</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>550</v>
+      </c>
+      <c r="B21" t="s">
+        <v>553</v>
+      </c>
+      <c r="C21" t="s">
+        <v>402</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>554</v>
+      </c>
+      <c r="B22" t="s">
+        <v>555</v>
+      </c>
+      <c r="C22" t="s">
+        <v>411</v>
+      </c>
+      <c r="E22" t="s">
+        <v>556</v>
+      </c>
+      <c r="F22" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>557</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KG/Batch_KG/sample_data/class_level_data_1.xlsx
+++ b/KG/Batch_KG/sample_data/class_level_data_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Iris\practice\GenAI\code\Batch_KG\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1593B267-6CFE-4DF5-8F2B-C85100CD29B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F06662E-3E53-408D-A0F4-195405F09018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" firstSheet="4" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" firstSheet="5" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JobGroups" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1127" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="565">
   <si>
     <t>id</t>
   </si>
@@ -1095,9 +1095,6 @@
     <t>US_2026_05</t>
   </si>
   <si>
-    <t>Independence Day (observed)</t>
-  </si>
-  <si>
     <t>US_2026_06</t>
   </si>
   <si>
@@ -1128,9 +1125,6 @@
     <t>CA</t>
   </si>
   <si>
-    <t>Family Day</t>
-  </si>
-  <si>
     <t>ALL_2026_01</t>
   </si>
   <si>
@@ -1149,18 +1143,9 @@
     <t>ALL_2026_03</t>
   </si>
   <si>
-    <t>Easter Monday</t>
-  </si>
-  <si>
-    <t>ALL_2026_04</t>
-  </si>
-  <si>
     <t>Christmas Day</t>
   </si>
   <si>
-    <t>ALL_2026_05</t>
-  </si>
-  <si>
     <t>Boxing Day</t>
   </si>
   <si>
@@ -1197,15 +1182,9 @@
     <t>CA_2026_04</t>
   </si>
   <si>
-    <t>Civic Holiday</t>
-  </si>
-  <si>
     <t>CA_2026_05</t>
   </si>
   <si>
-    <t>Labour Day</t>
-  </si>
-  <si>
     <t>CA_2026_06</t>
   </si>
   <si>
@@ -1260,9 +1239,6 @@
     <t>Nth Days-of-Week in Month</t>
   </si>
   <si>
-    <t>nth_dows_month</t>
-  </si>
-  <si>
     <t>PAT_NTH_DOM</t>
   </si>
   <si>
@@ -1272,9 +1248,6 @@
     <t>Nth Day-of-Month</t>
   </si>
   <si>
-    <t>daysOfMonth,occurrences</t>
-  </si>
-  <si>
     <t>nth_dom</t>
   </si>
   <si>
@@ -1368,45 +1341,6 @@
     <t>configParams</t>
   </si>
   <si>
-    <t>dayOfWeek,occurrences</t>
-  </si>
-  <si>
-    <t>Single day-of-week, specific Nth occurrences in a month</t>
-  </si>
-  <si>
-    <t>daysOfWeek,occurrences</t>
-  </si>
-  <si>
-    <t>Multiple days-of-week, specific Nth occurrences in a month</t>
-  </si>
-  <si>
-    <t>Specific calendar day numbers in specific months</t>
-  </si>
-  <si>
-    <t>occurrences</t>
-  </si>
-  <si>
-    <t>First business day of specific months; region excludes holidays</t>
-  </si>
-  <si>
-    <t>Last business day of specific months; region excludes holidays</t>
-  </si>
-  <si>
-    <t>First business day of specific quarters</t>
-  </si>
-  <si>
-    <t>Last business day of specific quarters</t>
-  </si>
-  <si>
-    <t>Single first business day of the calendar year</t>
-  </si>
-  <si>
-    <t>Single last business day of the calendar year</t>
-  </si>
-  <si>
-    <t>IS_HOLIDAY_ON edges queried with region IN [rule.region, 'ALL']</t>
-  </si>
-  <si>
     <t>ruleId</t>
   </si>
   <si>
@@ -1419,48 +1353,24 @@
     <t>Every 1st Sunday</t>
   </si>
   <si>
-    <t>{"dayOfWeek": 7, "occurrences": [1]}</t>
-  </si>
-  <si>
-    <t>1st Sunday of every month. Evaluator receives: date (runtime) + dayOfWeek/occurrences (from params)</t>
-  </si>
-  <si>
     <t>RULE_WEEKDAY</t>
   </si>
   <si>
     <t>Weekday</t>
   </si>
   <si>
-    <t>{"daysOfWeek": [1,2,3,4,5], "occurrences": [1,2,3,4,5]}</t>
-  </si>
-  <si>
-    <t>Any Monday–Friday. Evaluator receives: date (runtime) + daysOfWeek/occurrences (from params)</t>
-  </si>
-  <si>
     <t>RULE_WEEKEND</t>
   </si>
   <si>
     <t>Weekend</t>
   </si>
   <si>
-    <t>{"daysOfWeek": [6,7], "occurrences": [1,2,3,4,5]}</t>
-  </si>
-  <si>
-    <t>Any Saturday or Sunday. Evaluator receives: date (runtime) + daysOfWeek/occurrences (from params)</t>
-  </si>
-  <si>
     <t>RULE_1ST_2ND_WED</t>
   </si>
   <si>
     <t>Every 1st and 2nd Wednesday</t>
   </si>
   <si>
-    <t>{"dayOfWeek": 3, "occurrences": [1,2]}</t>
-  </si>
-  <si>
-    <t>1st and 2nd Wednesday of every month</t>
-  </si>
-  <si>
     <t>RULE_GLOBAL_HOLIDAYS</t>
   </si>
   <si>
@@ -1470,84 +1380,48 @@
     <t>{}</t>
   </si>
   <si>
-    <t>Universal market closures. Evaluator receives: date + region (both runtime); region=ALL</t>
-  </si>
-  <si>
     <t>RULE_CA_HOLIDAYS</t>
   </si>
   <si>
     <t>Canada Holidays</t>
   </si>
   <si>
-    <t>Canadian holidays. Evaluator receives: date + region (both runtime); region=CA</t>
-  </si>
-  <si>
     <t>RULE_1ST_BD_QUARTER</t>
   </si>
   <si>
     <t>Every 1st BD of Quarter</t>
   </si>
   <si>
-    <t>{"occurrences": [1,2,3,4]}</t>
-  </si>
-  <si>
-    <t>First business day of each quarter. Evaluator receives: date + region (runtime) + occurrences (from params)</t>
-  </si>
-  <si>
     <t>RULE_TUE_TO_FRI</t>
   </si>
   <si>
     <t>Every Tuesday to Friday</t>
   </si>
   <si>
-    <t>{"daysOfWeek": [2,3,4,5], "occurrences": [1,2,3,4,5]}</t>
-  </si>
-  <si>
-    <t>Any Tuesday–Friday</t>
-  </si>
-  <si>
     <t>RULE_1ST_4TH_SUNDAY</t>
   </si>
   <si>
     <t>Every 1st–4th Sunday</t>
   </si>
   <si>
-    <t>{"dayOfWeek": 7, "occurrences": [1,2,3,4]}</t>
-  </si>
-  <si>
-    <t>1st through 4th Sunday of every month</t>
-  </si>
-  <si>
     <t>RULE_US_HOLIDAYS</t>
   </si>
   <si>
     <t>US Holidays</t>
   </si>
   <si>
-    <t>US Federal holidays. Evaluator receives: date + region (both runtime); region=US</t>
-  </si>
-  <si>
     <t>RULE_FIRST_BD_MONTH</t>
   </si>
   <si>
     <t>First Business Day of Month</t>
   </si>
   <si>
-    <t>{"occurrences": [1,2,3,4,5,6,7,8,9,10,11,12]}</t>
-  </si>
-  <si>
-    <t>First BD of every month. Evaluator receives: date + region (runtime) + occurrences (from params)</t>
-  </si>
-  <si>
     <t>RULE_LAST_BD_MONTH</t>
   </si>
   <si>
     <t>Last Business Day of Month</t>
   </si>
   <si>
-    <t>Last BD of every month. Evaluator receives: date + region (runtime) + occurrences (from params)</t>
-  </si>
-  <si>
     <t>PAT_GRAPH_PROPERTY</t>
   </si>
   <si>
@@ -1563,63 +1437,42 @@
     <t>evaluate_graph_property</t>
   </si>
   <si>
-    <t>Reads a boolean property from any calendar hierarchy node (Day/Week/Month/Quarter/Year). Pure Python — computed from the date; no Neo4j lookup needed.</t>
-  </si>
-  <si>
     <t>RULE_FIRST_OF_MONTH</t>
   </si>
   <si>
     <t>First Day of Month</t>
   </si>
   <si>
-    <t>Matches the 1st calendar day of any month. Agent reads Day.isFirstOfMonth directly.</t>
-  </si>
-  <si>
     <t>RULE_LAST_OF_MONTH</t>
   </si>
   <si>
     <t>Last Day of Month</t>
   </si>
   <si>
-    <t>Matches the last calendar day of any month. Agent reads Day.isLastOfMonth directly.</t>
-  </si>
-  <si>
     <t>RULE_FIRST_OF_QUARTER</t>
   </si>
   <si>
     <t>First Day of Quarter</t>
   </si>
   <si>
-    <t>Matches Jan 1, Apr 1, Jul 1, Oct 1. Agent reads Day.isFirstOfQuarter directly.</t>
-  </si>
-  <si>
     <t>RULE_LAST_OF_QUARTER</t>
   </si>
   <si>
     <t>Last Day of Quarter</t>
   </si>
   <si>
-    <t>Matches Mar 31, Jun 30, Sep 30, Dec 31. Agent reads Day.isLastOfQuarter directly.</t>
-  </si>
-  <si>
     <t>RULE_FIRST_OF_YEAR</t>
   </si>
   <si>
     <t>First Day of Year</t>
   </si>
   <si>
-    <t>Matches January 1st. Agent reads Day.isFirstOfYear directly.</t>
-  </si>
-  <si>
     <t>RULE_LAST_OF_YEAR</t>
   </si>
   <si>
     <t>Last Day of Year</t>
   </si>
   <si>
-    <t>Matches December 31st. Agent reads Day.isLastOfYear directly.</t>
-  </si>
-  <si>
     <t>{"nodeName": "Day", "propertyName": "isFirstOfMonth"}</t>
   </si>
   <si>
@@ -1680,12 +1533,6 @@
     <t>targetDates</t>
   </si>
   <si>
-    <t>Matches any of a list of named holidays in the region. One rule covers multiple holidays — keeps catalog compact.</t>
-  </si>
-  <si>
-    <t>Matches any of a list of hardcoded dates. One rule covers multiple one-off blackouts. Year-specific — review annually.</t>
-  </si>
-  <si>
     <t>RULE_NewYear_AND_Christmas</t>
   </si>
   <si>
@@ -1695,18 +1542,9 @@
     <t>{"holidayNames": ["New Year's Day", "Christmas Day"]}</t>
   </si>
   <si>
-    <t>Matches New Year Day and Christmas Day directly</t>
-  </si>
-  <si>
     <t>RULE_TUE_TO_SAT</t>
   </si>
   <si>
-    <t>{"daysOfWeek": [2,3,4,5,6], "occurrences": [1,2,3,4,5]}</t>
-  </si>
-  <si>
-    <t>Any Tuesday–Saturday</t>
-  </si>
-  <si>
     <t>Every Tuesday to Saturday</t>
   </si>
   <si>
@@ -1716,10 +1554,193 @@
     <t>4th Business Day of Month</t>
   </si>
   <si>
-    <t>{"occurrences": [4]}</t>
-  </si>
-  <si>
-    <t>Fourth BD of every month. Evaluator receives: date + region (runtime) + occurrences (from params)</t>
+    <t>dayOfWeek,weekOccurrences,months</t>
+  </si>
+  <si>
+    <t>daysOfWeek,weekOccurrences,months</t>
+  </si>
+  <si>
+    <t>nth_multi_dow_month</t>
+  </si>
+  <si>
+    <t>daysOfMonth,months</t>
+  </si>
+  <si>
+    <t>months,bizDayFromStart</t>
+  </si>
+  <si>
+    <t>months,bizDayFromEnd</t>
+  </si>
+  <si>
+    <t>quarters,bizDayFromStart</t>
+  </si>
+  <si>
+    <t>quarters,bizDayFromEnd</t>
+  </si>
+  <si>
+    <t>{"dayOfWeek": 7, "weekOccurrences": [1], "months": []}</t>
+  </si>
+  <si>
+    <t>{"daysOfWeek": [1,2,3,4,5], "weekOccurrences": [1,2,3,4,5], "months": []}</t>
+  </si>
+  <si>
+    <t>{"daysOfWeek": [6,7], "weekOccurrences": [1,2,3,4,5], "months": []}</t>
+  </si>
+  <si>
+    <t>{"dayOfWeek": 3, "weekOccurrences": [1,2], "months": []}</t>
+  </si>
+  <si>
+    <t>{"daysOfWeek": [2,3,4,5], "weekOccurrences": [1,2,3,4,5], "months": []}</t>
+  </si>
+  <si>
+    <t>{"daysOfWeek": [2,3,4,5,6], "weekOccurrences": [1,2,3,4,5], "months": []}</t>
+  </si>
+  <si>
+    <t>{"dayOfWeek": 7, "weekOccurrences": [1,2,3,4], "months": []}</t>
+  </si>
+  <si>
+    <t>{"months": [], "bizDayFromStart": [1]}</t>
+  </si>
+  <si>
+    <t>{"months": [], "bizDayFromStart": [4]}</t>
+  </si>
+  <si>
+    <t>{"months": [], "bizDayFromEnd": [1]}</t>
+  </si>
+  <si>
+    <t>{"quarters": [], "bizDayFromStart": [1]}</t>
+  </si>
+  <si>
+    <t>RULE_LAST_BD_QUARTER</t>
+  </si>
+  <si>
+    <t>{"quarters": [], "bizDayFromEnd": [1]}</t>
+  </si>
+  <si>
+    <t>Last Business Day of Quarter</t>
+  </si>
+  <si>
+    <t>Matches a single weekday (dayOfWeek 1-7) on its Nth occurrence within the month (weekOccurrences 1-5). Optionally restricted to specific months (1-12); empty months = all months.</t>
+  </si>
+  <si>
+    <t>Matches any of a list of weekdays (daysOfWeek) on their Nth occurrence in the month (weekOccurrences 1-5). Optionally restricted to specific months; empty months = all months.</t>
+  </si>
+  <si>
+    <t>Matches specific calendar day numbers (daysOfMonth e.g. [1,15]). Optionally restricted to specific months (1-12); empty months = all months.</t>
+  </si>
+  <si>
+    <t>Matches the Nth business day(s) from the start of the month (bizDayFromStart e.g. [1]=1st BD, [4]=4th BD). Optionally restricted to specific months (1-12); empty months = all months. Region used by DENIES holiday rule.</t>
+  </si>
+  <si>
+    <t>Matches the Nth business day(s) from the end of the month (bizDayFromEnd e.g. [1]=last BD, [2]=2nd-to-last BD). Optionally restricted to specific months (1-12); empty months = all months.</t>
+  </si>
+  <si>
+    <t>Matches the Nth business day(s) from the start of the quarter (bizDayFromStart e.g. [1]=1st BD). Optionally restricted to specific quarters (1-4); empty quarters = all quarters.</t>
+  </si>
+  <si>
+    <t>Matches the Nth business day(s) from the end of the quarter (bizDayFromEnd e.g. [1]=last BD, [2]=2nd-to-last BD). Optionally restricted to specific quarters (1-4); empty quarters = all quarters.</t>
+  </si>
+  <si>
+    <t>Matches only the single first business day (Mon-Fri) of the calendar year. No configParams needed.</t>
+  </si>
+  <si>
+    <t>Matches only the single last business day (Mon-Fri) of the calendar year. No configParams needed.</t>
+  </si>
+  <si>
+    <t>IS_HOLIDAY_ON edges queried with region IN [rule.region, 'ALL']. Agent pre-fetches holiday_set and passes as runtime context. No configParams needed.</t>
+  </si>
+  <si>
+    <t>Reads a boolean structural property from a calendar hierarchy node (Day/Week/Month/Quarter/Year). Pure Python — computed from the date; no Neo4j lookup needed at eval time.</t>
+  </si>
+  <si>
+    <t>Matches any of a named list of holidays (holidayNames) in the given region. One rule can cover multiple holidays to keep the catalog compact.</t>
+  </si>
+  <si>
+    <t>Matches any of a list of hardcoded ISO dates (targetDates e.g. ["2026-03-15"]). Year-specific — review and update annually.</t>
+  </si>
+  <si>
+    <t>1st Sunday of every month. params: dayOfWeek=7, weekOccurrences=[1] (1st occurrence), months=[] (all months).</t>
+  </si>
+  <si>
+    <t>Any Monday–Friday, any week of any month. params: daysOfWeek=[1-5], weekOccurrences=[1,2,3,4,5], months=[] (all months).</t>
+  </si>
+  <si>
+    <t>Any Saturday or Sunday, any week of any month. params: daysOfWeek=[6,7], weekOccurrences=[1,2,3,4,5], months=[] (all months).</t>
+  </si>
+  <si>
+    <t>1st and 2nd Wednesday of every month. params: dayOfWeek=3, weekOccurrences=[1,2], months=[] (all months).</t>
+  </si>
+  <si>
+    <t>Any Tuesday–Friday, any week. params: daysOfWeek=[2,3,4,5], weekOccurrences=[1,2,3,4,5], months=[] (all months).</t>
+  </si>
+  <si>
+    <t>Any Tuesday–Saturday, any week. params: daysOfWeek=[2,3,4,5,6], weekOccurrences=[1,2,3,4,5], months=[] (all months).</t>
+  </si>
+  <si>
+    <t>1st through 4th Sunday of every month. params: dayOfWeek=7, weekOccurrences=[1,2,3,4], months=[] (all months).</t>
+  </si>
+  <si>
+    <t>Universal market closures. region=ALL — agent fetches holiday_set for ALL region at runtime. No configParams.</t>
+  </si>
+  <si>
+    <t>Canadian federal holidays. region=CA — agent fetches holiday_set for CA+ALL at runtime. No configParams.</t>
+  </si>
+  <si>
+    <t>US federal holidays. region=US — agent fetches holiday_set for US+ALL at runtime. No configParams.</t>
+  </si>
+  <si>
+    <t>First business day of every month. params: months=[] (all months), bizDayFromStart=[1] (1st BD from start).</t>
+  </si>
+  <si>
+    <t>4th business day of every month. params: months=[] (all months), bizDayFromStart=[4] (4th BD from start).</t>
+  </si>
+  <si>
+    <t>Last business day of every month. params: months=[] (all months), bizDayFromEnd=[1] (1st BD from end = last BD).</t>
+  </si>
+  <si>
+    <t>First business day of every quarter. params: quarters=[] (all quarters), bizDayFromStart=[1] (1st BD from start).</t>
+  </si>
+  <si>
+    <t>Last business day of every quarter. params: quarters=[] (all quarters), bizDayFromEnd=[1] (1st BD from end = last BD).</t>
+  </si>
+  <si>
+    <t>First calendar day of any month (Jan 1, Feb 1, …). params: nodeName=Day, propertyName=isFirstOfMonth.</t>
+  </si>
+  <si>
+    <t>Last calendar day of any month (Jan 31, Feb 28, …). params: nodeName=Day, propertyName=isLastOfMonth.</t>
+  </si>
+  <si>
+    <t>First calendar day of any quarter (Jan 1, Apr 1, Jul 1, Oct 1). params: nodeName=Day, propertyName=isFirstOfQuarter.</t>
+  </si>
+  <si>
+    <t>Last calendar day of any quarter (Mar 31, Jun 30, Sep 30, Dec 31). params: nodeName=Day, propertyName=isLastOfQuarter.</t>
+  </si>
+  <si>
+    <t>January 1st only. params: nodeName=Day, propertyName=isFirstOfYear.</t>
+  </si>
+  <si>
+    <t>December 31st only. params: nodeName=Day, propertyName=isLastOfYear.</t>
+  </si>
+  <si>
+    <t>Matches New Year's Day and Christmas Day in any region. params: holidayNames=["New Year's Day","Christmas Day"].</t>
+  </si>
+  <si>
+    <t>Thanksgiving</t>
+  </si>
+  <si>
+    <t>US_2026_10</t>
+  </si>
+  <si>
+    <t>US_2026_11</t>
+  </si>
+  <si>
+    <t>CA_2026_09</t>
+  </si>
+  <si>
+    <t>CA_2026_10</t>
+  </si>
+  <si>
+    <t>Independence Day</t>
   </si>
 </sst>
 </file>
@@ -1820,7 +1841,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1843,7 +1864,6 @@
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2563,7 +2583,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05669172-4566-411C-BAD9-C6B812325413}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
@@ -2595,12 +2615,12 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>533</v>
+        <v>484</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="B2" t="s">
         <v>96</v>
@@ -2620,7 +2640,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="B3" t="s">
         <v>97</v>
@@ -2640,7 +2660,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>490</v>
+        <v>452</v>
       </c>
       <c r="B4" t="s">
         <v>98</v>
@@ -2658,12 +2678,12 @@
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>530</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>509</v>
+        <v>465</v>
       </c>
       <c r="B5" t="s">
         <v>99</v>
@@ -2681,12 +2701,12 @@
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>531</v>
+        <v>482</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>506</v>
+        <v>463</v>
       </c>
       <c r="B6" t="s">
         <v>100</v>
@@ -2704,12 +2724,12 @@
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>532</v>
+        <v>483</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>490</v>
+        <v>452</v>
       </c>
       <c r="B7" t="s">
         <v>98</v>
@@ -2727,12 +2747,12 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>530</v>
+        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>490</v>
+        <v>452</v>
       </c>
       <c r="B8" t="s">
         <v>98</v>
@@ -2744,18 +2764,15 @@
         <v>287</v>
       </c>
       <c r="E8" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
-      </c>
-      <c r="G8" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="B9" t="s">
         <v>101</v>
@@ -2775,7 +2792,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="B10" t="s">
         <v>101</v>
@@ -2791,6 +2808,29 @@
       </c>
       <c r="F10" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>495</v>
+      </c>
+      <c r="B11" t="s">
+        <v>496</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
+        <v>287</v>
+      </c>
+      <c r="E11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -2801,11 +2841,11 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.453125" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.453125" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.08984375" bestFit="1" customWidth="1"/>
   </cols>
@@ -2814,11 +2854,11 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>391</v>
+      <c r="C1" s="10" t="s">
+        <v>384</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>1</v>
@@ -2826,121 +2866,121 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B2" s="9">
+        <v>46023</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="D2" t="s">
         <v>361</v>
-      </c>
-      <c r="B2" s="10">
-        <v>46023</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="D2" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B3" s="10">
-        <v>46115</v>
+        <v>367</v>
+      </c>
+      <c r="B3" s="9">
+        <v>46023</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="D3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>366</v>
-      </c>
-      <c r="B4" s="10">
-        <v>46118</v>
+        <v>357</v>
+      </c>
+      <c r="B4" s="9">
+        <v>46023</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D4" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>369</v>
+      </c>
+      <c r="B5" s="9">
+        <v>46041</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D5" t="s">
         <v>368</v>
-      </c>
-      <c r="B5" s="10">
-        <v>46381</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="D5" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>371</v>
+      </c>
+      <c r="B6" s="9">
+        <v>46069</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="D6" t="s">
         <v>370</v>
-      </c>
-      <c r="B6" s="10">
-        <v>46382</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>362</v>
-      </c>
-      <c r="D6" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>372</v>
-      </c>
-      <c r="B7" s="10">
-        <v>46041</v>
+        <v>373</v>
+      </c>
+      <c r="B7" s="9">
+        <v>46115</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="D7" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>375</v>
+      </c>
+      <c r="B8" s="9">
+        <v>46160</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="D8" t="s">
         <v>374</v>
-      </c>
-      <c r="B8" s="10">
-        <v>46069</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>346</v>
-      </c>
-      <c r="D8" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>376</v>
-      </c>
-      <c r="B9" s="10">
+        <v>345</v>
+      </c>
+      <c r="B9" s="9">
         <v>46167</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>346</v>
       </c>
       <c r="D9" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>345</v>
-      </c>
-      <c r="B10" s="10">
+        <v>348</v>
+      </c>
+      <c r="B10" s="9">
         <v>46192</v>
       </c>
       <c r="C10" s="9" t="s">
@@ -2952,184 +2992,212 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>348</v>
-      </c>
-      <c r="B11" s="10">
-        <v>46206</v>
+        <v>377</v>
+      </c>
+      <c r="B11" s="9">
+        <v>46204</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="D11" t="s">
-        <v>349</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>350</v>
-      </c>
-      <c r="B12" s="10">
-        <v>46272</v>
+        <v>349</v>
+      </c>
+      <c r="B12" s="9">
+        <v>46207</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>346</v>
       </c>
       <c r="D12" t="s">
-        <v>351</v>
+        <v>564</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>352</v>
-      </c>
-      <c r="B13" s="10">
-        <v>46307</v>
+        <v>362</v>
+      </c>
+      <c r="B13" s="9">
+        <v>46272</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="D13" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>354</v>
-      </c>
-      <c r="B14" s="10">
-        <v>46337</v>
+        <v>351</v>
+      </c>
+      <c r="B14" s="9">
+        <v>46272</v>
       </c>
       <c r="C14" s="9" t="s">
         <v>346</v>
       </c>
       <c r="D14" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>356</v>
-      </c>
-      <c r="B15" s="10">
-        <v>46352</v>
+        <v>378</v>
+      </c>
+      <c r="B15" s="9">
+        <v>46272</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="D15" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>379</v>
+      </c>
+      <c r="B16" s="9">
+        <v>46295</v>
+      </c>
+      <c r="C16" s="9" t="s">
         <v>358</v>
       </c>
-      <c r="B16" s="10">
-        <v>46069</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>359</v>
-      </c>
       <c r="D16" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>378</v>
-      </c>
-      <c r="B17" s="10">
-        <v>46160</v>
+        <v>353</v>
+      </c>
+      <c r="B17" s="9">
+        <v>46307</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="D17" t="s">
-        <v>379</v>
+        <v>352</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>380</v>
-      </c>
-      <c r="B18" s="10">
-        <v>46204</v>
+        <v>381</v>
+      </c>
+      <c r="B18" s="9">
+        <v>46307</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D18" t="s">
-        <v>381</v>
+        <v>559</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>382</v>
-      </c>
-      <c r="B19" s="10">
-        <v>46237</v>
+        <v>355</v>
+      </c>
+      <c r="B19" s="9">
+        <v>46337</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="D19" t="s">
-        <v>383</v>
+        <v>354</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>384</v>
-      </c>
-      <c r="B20" s="10">
-        <v>46272</v>
+        <v>382</v>
+      </c>
+      <c r="B20" s="9">
+        <v>46337</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D20" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>386</v>
-      </c>
-      <c r="B21" s="10">
-        <v>46295</v>
+        <v>560</v>
+      </c>
+      <c r="B21" s="9">
+        <v>46352</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="D21" t="s">
-        <v>387</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>388</v>
-      </c>
-      <c r="B22" s="10">
-        <v>46307</v>
+        <v>364</v>
+      </c>
+      <c r="B22" s="9">
+        <v>46381</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D22" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>389</v>
-      </c>
-      <c r="B23" s="10">
-        <v>46337</v>
+        <v>561</v>
+      </c>
+      <c r="B23" s="9">
+        <v>46381</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="D23" t="s">
-        <v>390</v>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>562</v>
+      </c>
+      <c r="B24" s="9">
+        <v>46381</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="D24" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>563</v>
+      </c>
+      <c r="B25" s="9">
+        <v>46382</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="D25" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -6013,407 +6081,407 @@
   <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="15.36328125" defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="6" width="15.36328125" style="15"/>
-    <col min="7" max="7" width="40.453125" style="15" customWidth="1"/>
-    <col min="8" max="8" width="7.1796875" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.90625" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="15.36328125" style="15"/>
+    <col min="1" max="6" width="15.36328125" style="14"/>
+    <col min="7" max="7" width="40.453125" style="14" customWidth="1"/>
+    <col min="8" max="8" width="7.1796875" style="14" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.90625" style="14" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="15.36328125" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="52" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" s="14" t="s">
         <v>392</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="D2" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>502</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="C1" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>438</v>
-      </c>
-      <c r="E1" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="G2" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="H2" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="52" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="G1" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="14" t="s">
+      <c r="B3" s="14" t="s">
         <v>395</v>
       </c>
-      <c r="I1" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>396</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="26" x14ac:dyDescent="0.3">
-      <c r="A2" s="15" t="s">
+      <c r="D3" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="G3" s="14" t="s">
+        <v>525</v>
+      </c>
+      <c r="H3" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="39" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="C4" s="14" t="s">
         <v>399</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D4" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>440</v>
-      </c>
-      <c r="F2" s="15" t="s">
+      <c r="E4" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="F4" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="G2" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="H2" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="26" x14ac:dyDescent="0.3">
-      <c r="A3" s="15" t="s">
+      <c r="G4" s="14" t="s">
+        <v>526</v>
+      </c>
+      <c r="H4" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="65" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D5" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>527</v>
+      </c>
+      <c r="H5" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="52" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>405</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>507</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>528</v>
+      </c>
+      <c r="H6" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="52" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
+        <v>409</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>410</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>508</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>529</v>
+      </c>
+      <c r="H7" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="52" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>509</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>530</v>
+      </c>
+      <c r="H8" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>531</v>
+      </c>
+      <c r="H9" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="26" x14ac:dyDescent="0.3">
+      <c r="A10" s="14" t="s">
+        <v>422</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>423</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="H10" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="52" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>427</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>428</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>533</v>
+      </c>
+      <c r="H11" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="65" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>458</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>459</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>443</v>
-      </c>
-      <c r="H3" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="26" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="D4" s="15" t="s">
+      <c r="E12" s="14" t="s">
+        <v>461</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>462</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>534</v>
+      </c>
+      <c r="H12" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="64" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
+        <v>485</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>486</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>493</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>487</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>535</v>
+      </c>
+      <c r="H13" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="48" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
+        <v>488</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="E4" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="F4" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>444</v>
-      </c>
-      <c r="H4" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="26" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="B5" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="E5" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>446</v>
-      </c>
-      <c r="H5" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="26" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>447</v>
-      </c>
-      <c r="H6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="26" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="E7" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="H7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="26" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>424</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="E8" s="15" t="s">
-        <v>445</v>
-      </c>
-      <c r="F8" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>449</v>
-      </c>
-      <c r="H8" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="26" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
-        <v>426</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>450</v>
-      </c>
-      <c r="H9" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="26" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>432</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="G10" s="15" t="s">
-        <v>451</v>
-      </c>
-      <c r="H10" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="26" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="B11" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>452</v>
-      </c>
-      <c r="H11" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="52" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
-        <v>500</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>501</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>502</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="15" t="s">
-        <v>503</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>504</v>
-      </c>
-      <c r="G12" s="15" t="s">
-        <v>505</v>
-      </c>
-      <c r="H12" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="48" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
-        <v>534</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>535</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>540</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>429</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>542</v>
-      </c>
-      <c r="F13" s="16" t="s">
+      <c r="E14" s="14" t="s">
+        <v>494</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="G14" s="15" t="s">
         <v>536</v>
       </c>
-      <c r="G13" s="16" t="s">
-        <v>544</v>
-      </c>
-      <c r="H13" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" s="15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="48" x14ac:dyDescent="0.3">
-      <c r="A14" s="16" t="s">
-        <v>537</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>538</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>541</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>543</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>539</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>545</v>
-      </c>
-      <c r="H14" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" s="15">
+      <c r="H14" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="14">
         <v>1</v>
       </c>
     </row>
@@ -6424,7 +6492,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A341CB3-E044-445E-8816-E6B6E23CAA09}">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultColWidth="26.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.1796875" bestFit="1" customWidth="1"/>
@@ -6433,224 +6501,224 @@
     <col min="4" max="4" width="6.08984375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="27.54296875" style="3" customWidth="1"/>
     <col min="6" max="6" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="41.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.36328125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="13" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>393</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>454</v>
-      </c>
-      <c r="F1" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="G1" s="12" t="s">
+    <row r="1" spans="1:7" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>431</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="G1" s="11" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>455</v>
+        <v>433</v>
       </c>
       <c r="B2" t="s">
-        <v>456</v>
+        <v>434</v>
       </c>
       <c r="C2" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>457</v>
+        <v>510</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>458</v>
+        <v>537</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="B3" t="s">
-        <v>460</v>
+        <v>436</v>
       </c>
       <c r="C3" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>461</v>
+        <v>511</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>462</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>463</v>
+        <v>437</v>
       </c>
       <c r="B4" t="s">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="C4" t="s">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>465</v>
+        <v>512</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>467</v>
+        <v>439</v>
       </c>
       <c r="B5" t="s">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="C5" t="s">
-        <v>398</v>
+        <v>391</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>469</v>
+        <v>513</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>471</v>
+        <v>448</v>
       </c>
       <c r="B6" t="s">
-        <v>472</v>
+        <v>449</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" t="s">
-        <v>362</v>
+        <v>395</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>473</v>
+        <v>514</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="B7" t="s">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D7" t="s">
-        <v>359</v>
+        <v>395</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>473</v>
+        <v>515</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>477</v>
+        <v>542</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>478</v>
+        <v>450</v>
       </c>
       <c r="B8" t="s">
-        <v>479</v>
+        <v>451</v>
       </c>
       <c r="C8" t="s">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>480</v>
+        <v>516</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>481</v>
+        <v>543</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>482</v>
+        <v>441</v>
       </c>
       <c r="B9" t="s">
-        <v>483</v>
+        <v>442</v>
       </c>
       <c r="C9" t="s">
-        <v>402</v>
+        <v>81</v>
+      </c>
+      <c r="D9" t="s">
+        <v>360</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>484</v>
+        <v>443</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>485</v>
+        <v>544</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>486</v>
+        <v>444</v>
       </c>
       <c r="B10" t="s">
-        <v>487</v>
+        <v>445</v>
       </c>
       <c r="C10" t="s">
-        <v>398</v>
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
+        <v>358</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>488</v>
+        <v>443</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>489</v>
+        <v>545</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>490</v>
+        <v>452</v>
       </c>
       <c r="B11" t="s">
-        <v>491</v>
+        <v>453</v>
       </c>
       <c r="C11" t="s">
         <v>81</v>
@@ -6659,239 +6727,257 @@
         <v>346</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>473</v>
+        <v>443</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>492</v>
+        <v>546</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>493</v>
+        <v>454</v>
       </c>
       <c r="B12" t="s">
-        <v>494</v>
+        <v>455</v>
       </c>
       <c r="C12" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>495</v>
+        <v>517</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>496</v>
+        <v>547</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B13" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C13" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>506</v>
+        <v>456</v>
       </c>
       <c r="B14" t="s">
-        <v>507</v>
+        <v>457</v>
       </c>
       <c r="C14" t="s">
-        <v>501</v>
+        <v>406</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>509</v>
+        <v>446</v>
       </c>
       <c r="B15" t="s">
-        <v>510</v>
+        <v>447</v>
       </c>
       <c r="C15" t="s">
-        <v>501</v>
+        <v>410</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>511</v>
+        <v>550</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="B16" t="s">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C16" t="s">
-        <v>501</v>
+        <v>414</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>514</v>
+        <v>551</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>515</v>
+        <v>463</v>
       </c>
       <c r="B17" t="s">
-        <v>516</v>
+        <v>464</v>
       </c>
       <c r="C17" t="s">
-        <v>501</v>
+        <v>459</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>527</v>
+        <v>475</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>517</v>
+        <v>552</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>518</v>
+        <v>465</v>
       </c>
       <c r="B18" t="s">
-        <v>519</v>
+        <v>466</v>
       </c>
       <c r="C18" t="s">
-        <v>501</v>
+        <v>459</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>528</v>
+        <v>476</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>520</v>
+        <v>553</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>521</v>
+        <v>467</v>
       </c>
       <c r="B19" t="s">
-        <v>522</v>
+        <v>468</v>
       </c>
       <c r="C19" t="s">
-        <v>501</v>
+        <v>459</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>529</v>
+        <v>477</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>546</v>
+        <v>469</v>
       </c>
       <c r="B20" t="s">
-        <v>547</v>
+        <v>470</v>
       </c>
       <c r="C20" t="s">
-        <v>535</v>
-      </c>
-      <c r="D20" t="s">
-        <v>362</v>
+        <v>459</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>548</v>
+        <v>478</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>550</v>
+        <v>471</v>
       </c>
       <c r="B21" t="s">
-        <v>553</v>
+        <v>472</v>
       </c>
       <c r="C21" t="s">
-        <v>402</v>
+        <v>459</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>551</v>
+        <v>479</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>554</v>
+        <v>473</v>
       </c>
       <c r="B22" t="s">
-        <v>555</v>
+        <v>474</v>
       </c>
       <c r="C22" t="s">
-        <v>411</v>
-      </c>
-      <c r="E22" t="s">
-        <v>556</v>
-      </c>
-      <c r="F22" s="3" t="b">
+        <v>459</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="F22" t="b">
         <v>1</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>557</v>
       </c>
     </row>
+    <row r="23" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>495</v>
+      </c>
+      <c r="B23" t="s">
+        <v>496</v>
+      </c>
+      <c r="C23" t="s">
+        <v>486</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>558</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/KG/Batch_KG/sample_data/class_level_data_1.xlsx
+++ b/KG/Batch_KG/sample_data/class_level_data_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Iris\practice\GenAI\code\Batch_KG\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F06662E-3E53-408D-A0F4-195405F09018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1B6364-EAFE-4C6C-9739-F084CFE549D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" firstSheet="5" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JobGroups" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1142" uniqueCount="565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1136" uniqueCount="566">
   <si>
     <t>id</t>
   </si>
@@ -339,9 +339,6 @@
     <t>Weekend Days</t>
   </si>
   <si>
-    <t>Business Hours</t>
-  </si>
-  <si>
     <t>Global Holidays in US</t>
   </si>
   <si>
@@ -1539,9 +1536,6 @@
     <t>New Year and Christmas</t>
   </si>
   <si>
-    <t>{"holidayNames": ["New Year's Day", "Christmas Day"]}</t>
-  </si>
-  <si>
     <t>RULE_TUE_TO_SAT</t>
   </si>
   <si>
@@ -1741,6 +1735,15 @@
   </si>
   <si>
     <t>Independence Day</t>
+  </si>
+  <si>
+    <t>JG_EOD,JG_TEST</t>
+  </si>
+  <si>
+    <t>JG_EOD,JG_MID</t>
+  </si>
+  <si>
+    <t>{"holidayDates": ["2026-01-01", "2026-12-25"]}</t>
   </si>
 </sst>
 </file>
@@ -2230,13 +2233,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B3" t="s">
         <v>268</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>269</v>
-      </c>
-      <c r="C3" t="s">
-        <v>270</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -2250,13 +2253,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" t="s">
         <v>287</v>
       </c>
-      <c r="B4" t="s">
-        <v>288</v>
-      </c>
       <c r="C4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -2265,18 +2268,18 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B5" t="s">
+        <v>298</v>
+      </c>
+      <c r="C5" t="s">
         <v>299</v>
-      </c>
-      <c r="C5" t="s">
-        <v>300</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -2285,18 +2288,18 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B6" t="s">
         <v>325</v>
       </c>
-      <c r="B6" t="s">
-        <v>326</v>
-      </c>
       <c r="C6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -2330,28 +2333,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>181</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>4</v>
@@ -2359,31 +2362,31 @@
     </row>
     <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
         <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H2" t="s">
+        <v>185</v>
+      </c>
+      <c r="I2" t="s">
         <v>186</v>
-      </c>
-      <c r="I2" t="s">
-        <v>187</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -2391,31 +2394,31 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C3" t="s">
         <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I3" t="s">
         <v>186</v>
-      </c>
-      <c r="I3" t="s">
-        <v>187</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -2423,31 +2426,31 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C4" t="s">
         <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -2455,31 +2458,31 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C5" t="s">
         <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -2487,28 +2490,28 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C6" t="s">
         <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -2516,28 +2519,28 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C7" t="s">
         <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F7" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -2545,31 +2548,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C8" t="s">
         <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -2583,7 +2586,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05669172-4566-411C-BAD9-C6B812325413}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
@@ -2609,18 +2612,18 @@
         <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B2" t="s">
         <v>96</v>
@@ -2640,16 +2643,16 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>5</v>
+        <v>563</v>
       </c>
       <c r="E3" t="s">
         <v>95</v>
@@ -2660,33 +2663,33 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>5</v>
+        <v>564</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>80</v>
@@ -2695,21 +2698,21 @@
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>80</v>
@@ -2718,50 +2721,47 @@
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
-      </c>
-      <c r="G7" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>452</v>
+        <v>434</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="E8" t="s">
         <v>95</v>
@@ -2772,65 +2772,45 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>435</v>
+        <v>494</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>495</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="E9" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G9" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>287</v>
+        <v>142</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>335</v>
       </c>
       <c r="E10" t="s">
         <v>95</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>495</v>
-      </c>
-      <c r="B11" t="s">
-        <v>496</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>287</v>
-      </c>
-      <c r="E11" t="s">
-        <v>103</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="s">
-        <v>481</v>
       </c>
     </row>
   </sheetData>
@@ -2858,7 +2838,7 @@
         <v>82</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>1</v>
@@ -2866,338 +2846,338 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B2" s="9">
         <v>46023</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="D2" t="s">
         <v>360</v>
-      </c>
-      <c r="D2" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B3" s="9">
         <v>46023</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B4" s="9">
         <v>46023</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B5" s="9">
         <v>46041</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B6" s="9">
         <v>46069</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B7" s="9">
         <v>46115</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B8" s="9">
         <v>46160</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B9" s="9">
         <v>46167</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B10" s="9">
         <v>46192</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D10" t="s">
         <v>346</v>
-      </c>
-      <c r="D10" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B11" s="9">
         <v>46204</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D11" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B12" s="9">
         <v>46207</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D12" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B13" s="9">
         <v>46272</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D13" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B14" s="9">
         <v>46272</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B15" s="9">
         <v>46272</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D15" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B16" s="9">
         <v>46295</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D16" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B17" s="9">
         <v>46307</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D17" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B18" s="9">
         <v>46307</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D18" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B19" s="9">
         <v>46337</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B20" s="9">
         <v>46337</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D20" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B21" s="9">
         <v>46352</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D21" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B22" s="9">
         <v>46381</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D22" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B23" s="9">
         <v>46381</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D23" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B24" s="9">
         <v>46381</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D24" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B25" s="9">
         <v>46382</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D25" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -3225,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -3236,376 +3216,376 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>231</v>
+      </c>
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" t="s">
         <v>232</v>
       </c>
-      <c r="B7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
         <v>233</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C10" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C11" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>273</v>
+      </c>
+      <c r="B15" t="s">
         <v>274</v>
       </c>
-      <c r="B15" t="s">
-        <v>275</v>
-      </c>
       <c r="C15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B16" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B17" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B18" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C18" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B20" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B21" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C22" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B23" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C23" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -3633,170 +3613,170 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>178</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>179</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>180</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G2" t="s">
         <v>183</v>
       </c>
-      <c r="F2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>184</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="J2" t="s">
         <v>185</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>186</v>
-      </c>
-      <c r="K2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H3" t="s">
         <v>189</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J3" t="s">
+        <v>185</v>
+      </c>
+      <c r="K3" t="s">
         <v>190</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K3" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G4" t="s">
         <v>183</v>
       </c>
-      <c r="F4" t="s">
-        <v>163</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>184</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="J4" t="s">
         <v>185</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="J4" t="s">
-        <v>186</v>
-      </c>
       <c r="K4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
+        <v>183</v>
+      </c>
+      <c r="E5" t="s">
+        <v>182</v>
+      </c>
+      <c r="F5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H5" t="s">
         <v>184</v>
       </c>
-      <c r="E5" t="s">
-        <v>183</v>
-      </c>
-      <c r="F5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G5" t="s">
-        <v>184</v>
-      </c>
-      <c r="H5" t="s">
-        <v>185</v>
-      </c>
       <c r="J5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="J6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>
@@ -3832,7 +3812,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -3973,13 +3953,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>326</v>
+      </c>
+      <c r="B10" t="s">
+        <v>326</v>
+      </c>
+      <c r="C10" t="s">
         <v>327</v>
-      </c>
-      <c r="B10" t="s">
-        <v>327</v>
-      </c>
-      <c r="C10" t="s">
-        <v>328</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -3990,13 +3970,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>328</v>
+      </c>
+      <c r="B11" t="s">
+        <v>328</v>
+      </c>
+      <c r="C11" t="s">
         <v>329</v>
-      </c>
-      <c r="B11" t="s">
-        <v>329</v>
-      </c>
-      <c r="C11" t="s">
-        <v>330</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -4007,13 +3987,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>330</v>
+      </c>
+      <c r="B12" t="s">
+        <v>330</v>
+      </c>
+      <c r="C12" t="s">
         <v>331</v>
-      </c>
-      <c r="B12" t="s">
-        <v>331</v>
-      </c>
-      <c r="C12" t="s">
-        <v>332</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -4024,13 +4004,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>332</v>
+      </c>
+      <c r="B13" t="s">
+        <v>332</v>
+      </c>
+      <c r="C13" t="s">
         <v>333</v>
-      </c>
-      <c r="B13" t="s">
-        <v>333</v>
-      </c>
-      <c r="C13" t="s">
-        <v>334</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -4057,7 +4037,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
@@ -4132,7 +4112,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -4140,7 +4120,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -4148,7 +4128,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -4156,7 +4136,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -4164,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -4172,7 +4152,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -4180,7 +4160,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -4188,7 +4168,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
@@ -4196,7 +4176,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
@@ -4204,7 +4184,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
@@ -4212,7 +4192,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
@@ -4220,7 +4200,7 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
@@ -4228,47 +4208,47 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B23" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B24" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B25" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B27" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -4303,10 +4283,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>20</v>
@@ -4315,7 +4295,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>2</v>
@@ -4323,10 +4303,10 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
@@ -4341,15 +4321,15 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
@@ -4364,15 +4344,15 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
@@ -4387,15 +4367,15 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
@@ -4410,15 +4390,15 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -4433,15 +4413,15 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
@@ -4456,12 +4436,12 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>29</v>
@@ -4479,12 +4459,12 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -4502,12 +4482,12 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>33</v>
@@ -4525,12 +4505,12 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>35</v>
@@ -4548,12 +4528,12 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>37</v>
@@ -4571,12 +4551,12 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -4594,12 +4574,12 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>41</v>
@@ -4617,12 +4597,12 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>43</v>
@@ -4640,12 +4620,12 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>45</v>
@@ -4663,187 +4643,187 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E17" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E18" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E19" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E20" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E21" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C22" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E22" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B24" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" t="s">
         <v>229</v>
       </c>
-      <c r="B24" t="s">
-        <v>171</v>
-      </c>
-      <c r="C24" t="s">
-        <v>230</v>
-      </c>
       <c r="E24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>339</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="C25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E25" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -4880,7 +4860,7 @@
         <v>94</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -4908,7 +4888,7 @@
         <v>86</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -4925,7 +4905,7 @@
         <v>86</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -4942,7 +4922,7 @@
         <v>87</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -4959,7 +4939,7 @@
         <v>88</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -4976,7 +4956,7 @@
         <v>89</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -4993,7 +4973,7 @@
         <v>91</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
@@ -5010,10 +4990,10 @@
         <v>95</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -5030,344 +5010,344 @@
         <v>83</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>95</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>95</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>95</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B27" t="s">
+        <v>326</v>
+      </c>
+      <c r="C27" t="s">
+        <v>324</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B27" t="s">
-        <v>327</v>
-      </c>
-      <c r="C27" t="s">
-        <v>325</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>337</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B28" t="s">
+        <v>328</v>
+      </c>
+      <c r="C28" t="s">
+        <v>324</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="B28" t="s">
-        <v>329</v>
-      </c>
-      <c r="C28" t="s">
-        <v>325</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="F28" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B29" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C29" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B30" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C30" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -5404,21 +5384,21 @@
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>90</v>
@@ -5427,21 +5407,21 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -5450,21 +5430,21 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>86</v>
@@ -5473,21 +5453,21 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -5496,53 +5476,53 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F6" s="3" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F7" s="3" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -5580,13 +5560,13 @@
         <v>51</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>52</v>
@@ -5618,7 +5598,7 @@
         <v>360000</v>
       </c>
       <c r="H2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I2" t="s">
         <v>70</v>
@@ -5644,7 +5624,7 @@
         <v>300000</v>
       </c>
       <c r="H3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I3" t="s">
         <v>70</v>
@@ -5670,7 +5650,7 @@
         <v>420000</v>
       </c>
       <c r="H4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I4" t="s">
         <v>70</v>
@@ -5693,16 +5673,16 @@
         <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F5">
         <v>600000</v>
       </c>
       <c r="H5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I5" t="s">
         <v>70</v>
@@ -5728,7 +5708,7 @@
         <v>300000</v>
       </c>
       <c r="H6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I6" t="s">
         <v>70</v>
@@ -5754,7 +5734,7 @@
         <v>540000</v>
       </c>
       <c r="H7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I7" t="s">
         <v>70</v>
@@ -5780,7 +5760,7 @@
         <v>240000</v>
       </c>
       <c r="H8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I8" t="s">
         <v>70</v>
@@ -5806,7 +5786,7 @@
         <v>360000</v>
       </c>
       <c r="H9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I9" t="s">
         <v>70</v>
@@ -5832,7 +5812,7 @@
         <v>3600000</v>
       </c>
       <c r="H10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I10" t="s">
         <v>70</v>
@@ -5852,7 +5832,7 @@
         <v>65</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>48</v>
@@ -5861,16 +5841,16 @@
         <v>47</v>
       </c>
       <c r="H11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I11" t="s">
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -5881,7 +5861,7 @@
         <v>66</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>48</v>
@@ -5890,16 +5870,16 @@
         <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I12" t="s">
         <v>8</v>
       </c>
       <c r="J12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -5910,25 +5890,25 @@
         <v>67</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G13" t="s">
         <v>47</v>
       </c>
       <c r="H13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I13" t="s">
         <v>8</v>
       </c>
       <c r="J13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -5936,10 +5916,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>48</v>
@@ -5948,16 +5928,16 @@
         <v>47</v>
       </c>
       <c r="H14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I14" t="s">
         <v>8</v>
       </c>
       <c r="J14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -5965,10 +5945,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C15" s="8">
         <v>0.29236111111111113</v>
@@ -5977,7 +5957,7 @@
         <v>47</v>
       </c>
       <c r="H15" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I15" t="s">
         <v>8</v>
@@ -5986,7 +5966,7 @@
         <v>80</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -5994,16 +5974,16 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F16">
         <v>3200000</v>
       </c>
       <c r="H16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I16" t="s">
         <v>70</v>
@@ -6012,7 +5992,7 @@
         <v>80</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -6020,16 +6000,16 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>295</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>297</v>
       </c>
       <c r="F17">
         <v>60000</v>
       </c>
       <c r="H17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I17" t="s">
         <v>70</v>
@@ -6038,7 +6018,7 @@
         <v>80</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -6046,16 +6026,16 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F18">
         <v>60000</v>
       </c>
       <c r="H18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I18" t="s">
         <v>70</v>
@@ -6064,7 +6044,7 @@
         <v>80</v>
       </c>
       <c r="K18" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -6090,54 +6070,54 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>386</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>430</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>387</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>388</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="52" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
+        <v>389</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="C2" s="14" t="s">
         <v>391</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>392</v>
       </c>
       <c r="D2" s="14" t="s">
         <v>82</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="H2" s="14" t="b">
         <v>1</v>
@@ -6148,25 +6128,25 @@
     </row>
     <row r="3" spans="1:9" ht="52" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
+        <v>393</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>395</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>396</v>
       </c>
       <c r="D3" s="14" t="s">
         <v>82</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="H3" s="14" t="b">
         <v>1</v>
@@ -6177,25 +6157,25 @@
     </row>
     <row r="4" spans="1:9" ht="39" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
+        <v>396</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="C4" s="14" t="s">
         <v>398</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>399</v>
       </c>
       <c r="D4" s="14" t="s">
         <v>82</v>
       </c>
       <c r="E4" s="14" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="H4" s="14" t="b">
         <v>1</v>
@@ -6206,25 +6186,25 @@
     </row>
     <row r="5" spans="1:9" ht="65" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>403</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>506</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>404</v>
-      </c>
       <c r="G5" s="14" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="H5" s="14" t="b">
         <v>1</v>
@@ -6235,25 +6215,25 @@
     </row>
     <row r="6" spans="1:9" ht="52" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
+        <v>404</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="C6" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>407</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>507</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>408</v>
-      </c>
       <c r="G6" s="14" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="H6" s="14" t="b">
         <v>1</v>
@@ -6264,25 +6244,25 @@
     </row>
     <row r="7" spans="1:9" ht="52" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
+        <v>408</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="C7" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>411</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>508</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>412</v>
-      </c>
       <c r="G7" s="14" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="H7" s="14" t="b">
         <v>1</v>
@@ -6293,25 +6273,25 @@
     </row>
     <row r="8" spans="1:9" ht="52" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
+        <v>412</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="C8" s="14" t="s">
         <v>414</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="D8" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>507</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>415</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>509</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>416</v>
-      </c>
       <c r="G8" s="14" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="H8" s="14" t="b">
         <v>1</v>
@@ -6322,22 +6302,22 @@
     </row>
     <row r="9" spans="1:9" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>417</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="F9" s="14" t="s">
         <v>420</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>421</v>
-      </c>
       <c r="G9" s="14" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="H9" s="14" t="b">
         <v>1</v>
@@ -6348,22 +6328,22 @@
     </row>
     <row r="10" spans="1:9" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
+        <v>421</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="D10" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>425</v>
-      </c>
       <c r="G10" s="14" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="H10" s="14" t="b">
         <v>1</v>
@@ -6374,22 +6354,22 @@
     </row>
     <row r="11" spans="1:9" ht="52" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B11" s="14" t="s">
         <v>81</v>
       </c>
       <c r="C11" s="14" t="s">
+        <v>426</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="F11" s="14" t="s">
         <v>427</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>428</v>
-      </c>
       <c r="G11" s="14" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="H11" s="14" t="b">
         <v>1</v>
@@ -6400,25 +6380,25 @@
     </row>
     <row r="12" spans="1:9" ht="65" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
+        <v>457</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="C12" s="14" t="s">
         <v>459</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>460</v>
       </c>
       <c r="D12" s="14" t="s">
         <v>82</v>
       </c>
       <c r="E12" s="14" t="s">
+        <v>460</v>
+      </c>
+      <c r="F12" s="14" t="s">
         <v>461</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>462</v>
-      </c>
       <c r="G12" s="14" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="H12" s="14" t="b">
         <v>1</v>
@@ -6429,25 +6409,25 @@
     </row>
     <row r="13" spans="1:9" ht="64" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
+        <v>484</v>
+      </c>
+      <c r="B13" s="14" t="s">
         <v>485</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="C13" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>419</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="F13" s="14" t="s">
         <v>486</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>491</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>420</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>487</v>
-      </c>
       <c r="G13" s="15" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="H13" s="14" t="b">
         <v>1</v>
@@ -6458,25 +6438,25 @@
     </row>
     <row r="14" spans="1:9" ht="48" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
+        <v>487</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>488</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>489</v>
-      </c>
       <c r="C14" s="14" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D14" s="14" t="s">
         <v>82</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="G14" s="15" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="H14" s="14" t="b">
         <v>1</v>
@@ -6506,22 +6486,22 @@
   <sheetData>
     <row r="1" spans="1:7" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
+        <v>430</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>431</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>386</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>384</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>432</v>
-      </c>
       <c r="F1" s="11" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>2</v>
@@ -6529,451 +6509,451 @@
     </row>
     <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B2" t="s">
         <v>433</v>
       </c>
-      <c r="B2" t="s">
-        <v>434</v>
-      </c>
       <c r="C2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B3" t="s">
         <v>435</v>
       </c>
-      <c r="B3" t="s">
-        <v>436</v>
-      </c>
       <c r="C3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B4" t="s">
         <v>437</v>
       </c>
-      <c r="B4" t="s">
-        <v>438</v>
-      </c>
       <c r="C4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>438</v>
+      </c>
+      <c r="B5" t="s">
         <v>439</v>
       </c>
-      <c r="B5" t="s">
-        <v>440</v>
-      </c>
       <c r="C5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>447</v>
+      </c>
+      <c r="B6" t="s">
         <v>448</v>
       </c>
-      <c r="B6" t="s">
-        <v>449</v>
-      </c>
       <c r="C6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B7" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>449</v>
+      </c>
+      <c r="B8" t="s">
         <v>450</v>
       </c>
-      <c r="B8" t="s">
-        <v>451</v>
-      </c>
       <c r="C8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>440</v>
+      </c>
+      <c r="B9" t="s">
         <v>441</v>
-      </c>
-      <c r="B9" t="s">
-        <v>442</v>
       </c>
       <c r="C9" t="s">
         <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>443</v>
+      </c>
+      <c r="B10" t="s">
         <v>444</v>
-      </c>
-      <c r="B10" t="s">
-        <v>445</v>
       </c>
       <c r="C10" t="s">
         <v>81</v>
       </c>
       <c r="D10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>451</v>
+      </c>
+      <c r="B11" t="s">
         <v>452</v>
-      </c>
-      <c r="B11" t="s">
-        <v>453</v>
       </c>
       <c r="C11" t="s">
         <v>81</v>
       </c>
       <c r="D11" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>453</v>
+      </c>
+      <c r="B12" t="s">
         <v>454</v>
       </c>
-      <c r="B12" t="s">
-        <v>455</v>
-      </c>
       <c r="C12" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B13" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="C13" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>455</v>
+      </c>
+      <c r="B14" t="s">
         <v>456</v>
       </c>
-      <c r="B14" t="s">
-        <v>457</v>
-      </c>
       <c r="C14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>445</v>
+      </c>
+      <c r="B15" t="s">
         <v>446</v>
       </c>
-      <c r="B15" t="s">
-        <v>447</v>
-      </c>
       <c r="C15" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>519</v>
+      </c>
+      <c r="B16" t="s">
         <v>521</v>
       </c>
-      <c r="B16" t="s">
-        <v>523</v>
-      </c>
       <c r="C16" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>462</v>
+      </c>
+      <c r="B17" t="s">
         <v>463</v>
       </c>
-      <c r="B17" t="s">
-        <v>464</v>
-      </c>
       <c r="C17" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>464</v>
+      </c>
+      <c r="B18" t="s">
         <v>465</v>
       </c>
-      <c r="B18" t="s">
-        <v>466</v>
-      </c>
       <c r="C18" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>466</v>
+      </c>
+      <c r="B19" t="s">
         <v>467</v>
       </c>
-      <c r="B19" t="s">
-        <v>468</v>
-      </c>
       <c r="C19" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>468</v>
+      </c>
+      <c r="B20" t="s">
         <v>469</v>
       </c>
-      <c r="B20" t="s">
-        <v>470</v>
-      </c>
       <c r="C20" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>470</v>
+      </c>
+      <c r="B21" t="s">
         <v>471</v>
       </c>
-      <c r="B21" t="s">
-        <v>472</v>
-      </c>
       <c r="C21" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>472</v>
+      </c>
+      <c r="B22" t="s">
         <v>473</v>
       </c>
-      <c r="B22" t="s">
-        <v>474</v>
-      </c>
       <c r="C22" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>494</v>
+      </c>
+      <c r="B23" t="s">
         <v>495</v>
       </c>
-      <c r="B23" t="s">
-        <v>496</v>
-      </c>
       <c r="C23" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>497</v>
+        <v>565</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
   </sheetData>

--- a/KG/Batch_KG/sample_data/class_level_data_1.xlsx
+++ b/KG/Batch_KG/sample_data/class_level_data_1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Iris\practice\GenAI\code\Batch_KG\sample_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1B6364-EAFE-4C6C-9739-F084CFE549D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0AAC667-5429-4296-8D88-F746C03A417B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="736" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="JobGroups" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,9 @@
     <sheet name="ResourceDependency" sheetId="6" r:id="rId6"/>
     <sheet name="SLAs" sheetId="8" r:id="rId7"/>
     <sheet name="CalendarPatterns" sheetId="9" r:id="rId8"/>
-    <sheet name="JobRules" sheetId="18" r:id="rId9"/>
+    <sheet name="BusinessCalendars" sheetId="18" r:id="rId9"/>
     <sheet name="DataInteraction_v2" sheetId="15" state="hidden" r:id="rId10"/>
-    <sheet name="JobRulesAssociation" sheetId="12" r:id="rId11"/>
+    <sheet name="BusinessCalendarsAssociation" sheetId="12" r:id="rId11"/>
     <sheet name="Holidays" sheetId="10" r:id="rId12"/>
     <sheet name="Tags" sheetId="16" r:id="rId13"/>
     <sheet name="DataInteraction_v1" sheetId="14" state="hidden" r:id="rId14"/>
@@ -261,9 +261,6 @@
     <t>HIGH</t>
   </si>
   <si>
-    <t>Job</t>
-  </si>
-  <si>
     <t>SLA_AR-ML-LS2-TRIGGER</t>
   </si>
   <si>
@@ -1744,6 +1741,9 @@
   </si>
   <si>
     <t>{"holidayDates": ["2026-01-01", "2026-12-25"]}</t>
+  </si>
+  <si>
+    <t>ScheduledInstanceContext</t>
   </si>
 </sst>
 </file>
@@ -2211,7 +2211,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -2233,13 +2233,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B3" t="s">
         <v>267</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>268</v>
-      </c>
-      <c r="C3" t="s">
-        <v>269</v>
       </c>
       <c r="D3" t="s">
         <v>8</v>
@@ -2253,13 +2253,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B4" t="s">
         <v>286</v>
       </c>
-      <c r="B4" t="s">
-        <v>287</v>
-      </c>
       <c r="C4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D4" t="s">
         <v>8</v>
@@ -2268,18 +2268,18 @@
         <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C5" t="s">
         <v>298</v>
-      </c>
-      <c r="C5" t="s">
-        <v>299</v>
       </c>
       <c r="D5" t="s">
         <v>8</v>
@@ -2288,18 +2288,18 @@
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B6" t="s">
         <v>324</v>
       </c>
-      <c r="B6" t="s">
-        <v>325</v>
-      </c>
       <c r="C6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -2333,28 +2333,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>172</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>180</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>4</v>
@@ -2362,31 +2362,31 @@
     </row>
     <row r="2" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C2" t="s">
         <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I2" t="s">
         <v>185</v>
-      </c>
-      <c r="I2" t="s">
-        <v>186</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
@@ -2394,31 +2394,31 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C3" t="s">
         <v>68</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I3" t="s">
         <v>185</v>
-      </c>
-      <c r="I3" t="s">
-        <v>186</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
@@ -2426,31 +2426,31 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C4" t="s">
         <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
@@ -2458,31 +2458,31 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C5" t="s">
         <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
@@ -2490,28 +2490,28 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C6" t="s">
         <v>68</v>
       </c>
       <c r="D6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
@@ -2519,28 +2519,28 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C7" t="s">
         <v>68</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H7" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
@@ -2548,31 +2548,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C8" t="s">
         <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I8" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
@@ -2609,33 +2609,33 @@
         <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D2" t="s">
         <v>5</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -2643,19 +2643,19 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -2663,88 +2663,88 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
         <v>5</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -2752,19 +2752,19 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -2772,42 +2772,42 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9" t="s">
         <v>494</v>
       </c>
-      <c r="B9" t="s">
-        <v>495</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B10" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -2835,10 +2835,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>1</v>
@@ -2846,338 +2846,338 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B2" s="9">
         <v>46023</v>
       </c>
       <c r="C2" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="D2" t="s">
         <v>359</v>
-      </c>
-      <c r="D2" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B3" s="9">
         <v>46023</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B4" s="9">
         <v>46023</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B5" s="9">
         <v>46041</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B6" s="9">
         <v>46069</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B7" s="9">
         <v>46115</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D7" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B8" s="9">
         <v>46160</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D8" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B9" s="9">
         <v>46167</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B10" s="9">
         <v>46192</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="D10" t="s">
         <v>345</v>
-      </c>
-      <c r="D10" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B11" s="9">
         <v>46204</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D11" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B12" s="9">
         <v>46207</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D12" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B13" s="9">
         <v>46272</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B14" s="9">
         <v>46272</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B15" s="9">
         <v>46272</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D15" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B16" s="9">
         <v>46295</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D16" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B17" s="9">
         <v>46307</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D17" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B18" s="9">
         <v>46307</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D18" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B19" s="9">
         <v>46337</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D19" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B20" s="9">
         <v>46337</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D20" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B21" s="9">
         <v>46352</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D21" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B22" s="9">
         <v>46381</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D22" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B23" s="9">
         <v>46381</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D23" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B24" s="9">
         <v>46381</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D24" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B25" s="9">
         <v>46382</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D25" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -3205,7 +3205,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>4</v>
@@ -3216,376 +3216,376 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D3" t="b">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D4" t="b">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>230</v>
+      </c>
+      <c r="B7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" t="s">
         <v>231</v>
       </c>
-      <c r="B7" t="s">
-        <v>158</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
         <v>232</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C11" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D14" t="b">
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>272</v>
+      </c>
+      <c r="B15" t="s">
         <v>273</v>
       </c>
-      <c r="B15" t="s">
-        <v>274</v>
-      </c>
       <c r="C15" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D15" t="b">
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D16" t="b">
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B17" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D17" t="b">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B18" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C18" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D18" t="b">
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D19" t="b">
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B20" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D20" t="b">
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B21" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C21" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D21" t="b">
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D22" t="b">
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C23" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D23" t="b">
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -3613,170 +3613,170 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>178</v>
       </c>
       <c r="I1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
         <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G2" t="s">
         <v>182</v>
       </c>
-      <c r="F2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>183</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J2" t="s">
         <v>184</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>185</v>
-      </c>
-      <c r="K2" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B3" t="s">
         <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H3" t="s">
         <v>188</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="J3" t="s">
+        <v>184</v>
+      </c>
+      <c r="K3" t="s">
         <v>189</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J3" t="s">
-        <v>185</v>
-      </c>
-      <c r="K3" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F4" t="s">
+        <v>161</v>
+      </c>
+      <c r="G4" t="s">
         <v>182</v>
       </c>
-      <c r="F4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>183</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J4" t="s">
         <v>184</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J4" t="s">
-        <v>185</v>
-      </c>
       <c r="K4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
+        <v>182</v>
+      </c>
+      <c r="E5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G5" t="s">
+        <v>182</v>
+      </c>
+      <c r="H5" t="s">
         <v>183</v>
       </c>
-      <c r="E5" t="s">
-        <v>182</v>
-      </c>
-      <c r="F5" t="s">
-        <v>160</v>
-      </c>
-      <c r="G5" t="s">
-        <v>183</v>
-      </c>
-      <c r="H5" t="s">
-        <v>184</v>
-      </c>
       <c r="J5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="J6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -3812,7 +3812,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -3953,13 +3953,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>325</v>
+      </c>
+      <c r="B10" t="s">
+        <v>325</v>
+      </c>
+      <c r="C10" t="s">
         <v>326</v>
-      </c>
-      <c r="B10" t="s">
-        <v>326</v>
-      </c>
-      <c r="C10" t="s">
-        <v>327</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -3970,13 +3970,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>327</v>
+      </c>
+      <c r="B11" t="s">
+        <v>327</v>
+      </c>
+      <c r="C11" t="s">
         <v>328</v>
-      </c>
-      <c r="B11" t="s">
-        <v>328</v>
-      </c>
-      <c r="C11" t="s">
-        <v>329</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -3987,13 +3987,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>329</v>
+      </c>
+      <c r="B12" t="s">
+        <v>329</v>
+      </c>
+      <c r="C12" t="s">
         <v>330</v>
-      </c>
-      <c r="B12" t="s">
-        <v>330</v>
-      </c>
-      <c r="C12" t="s">
-        <v>331</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -4004,13 +4004,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>331</v>
+      </c>
+      <c r="B13" t="s">
+        <v>331</v>
+      </c>
+      <c r="C13" t="s">
         <v>332</v>
-      </c>
-      <c r="B13" t="s">
-        <v>332</v>
-      </c>
-      <c r="C13" t="s">
-        <v>333</v>
       </c>
       <c r="D13" t="b">
         <v>1</v>
@@ -4037,7 +4037,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
@@ -4112,7 +4112,7 @@
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -4120,7 +4120,7 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -4128,7 +4128,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -4136,7 +4136,7 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -4144,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
@@ -4152,7 +4152,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
@@ -4160,7 +4160,7 @@
         <v>11</v>
       </c>
       <c r="B16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
@@ -4168,7 +4168,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
@@ -4176,7 +4176,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
@@ -4184,7 +4184,7 @@
         <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
@@ -4192,7 +4192,7 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
@@ -4200,7 +4200,7 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
@@ -4208,47 +4208,47 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B23" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B24" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B25" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B27" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
   </sheetData>
@@ -4283,10 +4283,10 @@
         <v>19</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>20</v>
@@ -4295,7 +4295,7 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I1" s="7" t="s">
         <v>2</v>
@@ -4303,10 +4303,10 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
@@ -4321,15 +4321,15 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
         <v>22</v>
@@ -4344,15 +4344,15 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
@@ -4367,15 +4367,15 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C5" t="s">
         <v>22</v>
@@ -4390,15 +4390,15 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
@@ -4413,15 +4413,15 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
@@ -4436,12 +4436,12 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>29</v>
@@ -4459,12 +4459,12 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>31</v>
@@ -4482,12 +4482,12 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>33</v>
@@ -4505,12 +4505,12 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>35</v>
@@ -4528,12 +4528,12 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>37</v>
@@ -4551,12 +4551,12 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -4574,12 +4574,12 @@
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>41</v>
@@ -4597,12 +4597,12 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>43</v>
@@ -4620,12 +4620,12 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>45</v>
@@ -4643,187 +4643,187 @@
         <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E18" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E19" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G20" t="b">
         <v>1</v>
       </c>
       <c r="H20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C21" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E21" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G21" t="b">
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C22" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E22" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E23" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G23" t="b">
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>227</v>
+      </c>
+      <c r="B24" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" t="s">
         <v>228</v>
       </c>
-      <c r="B24" t="s">
-        <v>170</v>
-      </c>
-      <c r="C24" t="s">
-        <v>229</v>
-      </c>
       <c r="E24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G24" t="b">
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>338</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>340</v>
-      </c>
       <c r="C25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E25" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
       <c r="H25" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>
@@ -4854,18 +4854,18 @@
         <v>9</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="F1" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>17</v>
@@ -4876,7 +4876,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
@@ -4885,15 +4885,15 @@
         <v>5</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>13</v>
@@ -4902,15 +4902,15 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>14</v>
@@ -4919,15 +4919,15 @@
         <v>5</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>16</v>
@@ -4936,15 +4936,15 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
@@ -4953,15 +4953,15 @@
         <v>5</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>15</v>
@@ -4970,15 +4970,15 @@
         <v>5</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>11</v>
@@ -4987,18 +4987,18 @@
         <v>5</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>18</v>
@@ -5007,347 +5007,347 @@
         <v>5</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C12" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C16" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C20" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C21" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="C26" t="s">
+        <v>323</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C26" t="s">
-        <v>324</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>335</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B27" t="s">
+        <v>325</v>
+      </c>
+      <c r="C27" t="s">
+        <v>323</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="B27" t="s">
-        <v>326</v>
-      </c>
-      <c r="C27" t="s">
-        <v>324</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>336</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="B28" t="s">
+        <v>327</v>
+      </c>
+      <c r="C28" t="s">
+        <v>323</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B28" t="s">
-        <v>328</v>
-      </c>
-      <c r="C28" t="s">
-        <v>324</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>337</v>
-      </c>
       <c r="F28" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B29" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C29" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B30" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C30" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -5378,50 +5378,50 @@
         <v>46</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F2" s="3" t="b">
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
         <v>5</v>
@@ -5430,44 +5430,44 @@
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F4" s="3" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E5" t="s">
         <v>5</v>
@@ -5476,53 +5476,53 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F6" s="3" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F7" s="3" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -5544,7 +5544,7 @@
     <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.08984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="34.7265625" style="3" customWidth="1"/>
     <col min="12" max="12" width="8.26953125" bestFit="1" customWidth="1"/>
   </cols>
@@ -5560,13 +5560,13 @@
         <v>51</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>52</v>
@@ -5598,16 +5598,16 @@
         <v>360000</v>
       </c>
       <c r="H2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I2" t="s">
         <v>70</v>
       </c>
       <c r="J2" t="s">
-        <v>71</v>
+        <v>565</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="L2" t="b">
         <v>1</v>
@@ -5618,22 +5618,22 @@
         <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F3">
         <v>300000</v>
       </c>
       <c r="H3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I3" t="s">
         <v>70</v>
       </c>
       <c r="J3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>12</v>
+        <v>565</v>
+      </c>
+      <c r="K3" t="s">
+        <v>83</v>
       </c>
       <c r="L3" t="b">
         <v>1</v>
@@ -5644,22 +5644,22 @@
         <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F4">
         <v>420000</v>
       </c>
       <c r="H4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I4" t="s">
         <v>70</v>
       </c>
       <c r="J4" t="s">
-        <v>71</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>13</v>
+        <v>565</v>
+      </c>
+      <c r="K4" t="s">
+        <v>84</v>
       </c>
       <c r="L4" t="b">
         <v>1</v>
@@ -5670,28 +5670,28 @@
         <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F5">
         <v>600000</v>
       </c>
       <c r="H5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I5" t="s">
         <v>70</v>
       </c>
       <c r="J5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>14</v>
+        <v>565</v>
+      </c>
+      <c r="K5" t="s">
+        <v>85</v>
       </c>
       <c r="L5" t="b">
         <v>1</v>
@@ -5702,22 +5702,22 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F6">
         <v>300000</v>
       </c>
       <c r="H6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I6" t="s">
         <v>70</v>
       </c>
       <c r="J6" t="s">
-        <v>71</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>15</v>
+        <v>565</v>
+      </c>
+      <c r="K6" t="s">
+        <v>88</v>
       </c>
       <c r="L6" t="b">
         <v>1</v>
@@ -5728,22 +5728,22 @@
         <v>61</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F7">
         <v>540000</v>
       </c>
       <c r="H7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I7" t="s">
         <v>70</v>
       </c>
       <c r="J7" t="s">
-        <v>71</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>16</v>
+        <v>565</v>
+      </c>
+      <c r="K7" t="s">
+        <v>86</v>
       </c>
       <c r="L7" t="b">
         <v>1</v>
@@ -5754,22 +5754,22 @@
         <v>62</v>
       </c>
       <c r="B8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F8">
         <v>240000</v>
       </c>
       <c r="H8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I8" t="s">
         <v>70</v>
       </c>
       <c r="J8" t="s">
-        <v>71</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>17</v>
+        <v>565</v>
+      </c>
+      <c r="K8" t="s">
+        <v>82</v>
       </c>
       <c r="L8" t="b">
         <v>1</v>
@@ -5780,22 +5780,22 @@
         <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F9">
         <v>360000</v>
       </c>
       <c r="H9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I9" t="s">
         <v>70</v>
       </c>
       <c r="J9" t="s">
-        <v>71</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>18</v>
+        <v>565</v>
+      </c>
+      <c r="K9" t="s">
+        <v>90</v>
       </c>
       <c r="L9" t="b">
         <v>1</v>
@@ -5806,19 +5806,19 @@
         <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F10">
         <v>3600000</v>
       </c>
       <c r="H10" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I10" t="s">
         <v>70</v>
       </c>
       <c r="J10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -5832,7 +5832,7 @@
         <v>65</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>48</v>
@@ -5841,16 +5841,16 @@
         <v>47</v>
       </c>
       <c r="H11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I11" t="s">
         <v>8</v>
       </c>
       <c r="J11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L11" t="b">
         <v>1</v>
@@ -5861,7 +5861,7 @@
         <v>66</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>48</v>
@@ -5870,16 +5870,16 @@
         <v>47</v>
       </c>
       <c r="H12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I12" t="s">
         <v>8</v>
       </c>
       <c r="J12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -5890,25 +5890,25 @@
         <v>67</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G13" t="s">
         <v>47</v>
       </c>
       <c r="H13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I13" t="s">
         <v>8</v>
       </c>
       <c r="J13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L13" t="b">
         <v>1</v>
@@ -5916,10 +5916,10 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>48</v>
@@ -5928,16 +5928,16 @@
         <v>47</v>
       </c>
       <c r="H14" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I14" t="s">
         <v>8</v>
       </c>
       <c r="J14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L14" t="b">
         <v>1</v>
@@ -5945,10 +5945,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C15" s="8">
         <v>0.29236111111111113</v>
@@ -5957,16 +5957,16 @@
         <v>47</v>
       </c>
       <c r="H15" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I15" t="s">
         <v>8</v>
       </c>
       <c r="J15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -5974,25 +5974,25 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F16">
         <v>3200000</v>
       </c>
       <c r="H16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I16" t="s">
         <v>70</v>
       </c>
       <c r="J16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="L16" t="b">
         <v>1</v>
@@ -6000,25 +6000,25 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>294</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>295</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>296</v>
       </c>
       <c r="F17">
         <v>60000</v>
       </c>
       <c r="H17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I17" t="s">
         <v>70</v>
       </c>
       <c r="J17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -6026,25 +6026,25 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F18">
         <v>60000</v>
       </c>
       <c r="H18" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I18" t="s">
         <v>70</v>
       </c>
       <c r="J18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K18" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="L18" t="b">
         <v>1</v>
@@ -6070,54 +6070,54 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>384</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>385</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>386</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>2</v>
       </c>
       <c r="H1" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>387</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="52" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
+        <v>388</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>389</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="C2" s="14" t="s">
         <v>390</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>499</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>391</v>
       </c>
-      <c r="D2" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>500</v>
-      </c>
-      <c r="F2" s="14" t="s">
-        <v>392</v>
-      </c>
       <c r="G2" s="14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H2" s="14" t="b">
         <v>1</v>
@@ -6128,25 +6128,25 @@
     </row>
     <row r="3" spans="1:9" ht="52" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
+        <v>392</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>393</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="C3" s="14" t="s">
         <v>394</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>395</v>
-      </c>
       <c r="D3" s="14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E3" s="14" t="s">
+        <v>500</v>
+      </c>
+      <c r="F3" s="14" t="s">
         <v>501</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>502</v>
-      </c>
       <c r="G3" s="14" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H3" s="14" t="b">
         <v>1</v>
@@ -6157,25 +6157,25 @@
     </row>
     <row r="4" spans="1:9" ht="39" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
+        <v>395</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>396</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="C4" s="14" t="s">
         <v>397</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="D4" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>502</v>
+      </c>
+      <c r="F4" s="14" t="s">
         <v>398</v>
       </c>
-      <c r="D4" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>503</v>
-      </c>
-      <c r="F4" s="14" t="s">
-        <v>399</v>
-      </c>
       <c r="G4" s="14" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H4" s="14" t="b">
         <v>1</v>
@@ -6186,25 +6186,25 @@
     </row>
     <row r="5" spans="1:9" ht="65" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
         <v>401</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>503</v>
+      </c>
+      <c r="F5" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="D5" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>504</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>403</v>
-      </c>
       <c r="G5" s="14" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H5" s="14" t="b">
         <v>1</v>
@@ -6215,25 +6215,25 @@
     </row>
     <row r="6" spans="1:9" ht="52" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>404</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="C6" s="14" t="s">
         <v>405</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>504</v>
+      </c>
+      <c r="F6" s="14" t="s">
         <v>406</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>505</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>407</v>
-      </c>
       <c r="G6" s="14" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H6" s="14" t="b">
         <v>1</v>
@@ -6244,25 +6244,25 @@
     </row>
     <row r="7" spans="1:9" ht="52" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>408</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="C7" s="14" t="s">
         <v>409</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>505</v>
+      </c>
+      <c r="F7" s="14" t="s">
         <v>410</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>506</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>411</v>
-      </c>
       <c r="G7" s="14" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H7" s="14" t="b">
         <v>1</v>
@@ -6273,25 +6273,25 @@
     </row>
     <row r="8" spans="1:9" ht="52" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
+        <v>411</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>412</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="C8" s="14" t="s">
         <v>413</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="D8" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>506</v>
+      </c>
+      <c r="F8" s="14" t="s">
         <v>414</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>507</v>
-      </c>
-      <c r="F8" s="14" t="s">
-        <v>415</v>
-      </c>
       <c r="G8" s="14" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H8" s="14" t="b">
         <v>1</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="9" spans="1:9" ht="26" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>416</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="14" t="s">
         <v>417</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="F9" s="14" t="s">
         <v>419</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>420</v>
-      </c>
       <c r="G9" s="14" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H9" s="14" t="b">
         <v>1</v>
@@ -6328,22 +6328,22 @@
     </row>
     <row r="10" spans="1:9" ht="26" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
+        <v>420</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>421</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="14" t="s">
         <v>422</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="D10" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>423</v>
       </c>
-      <c r="D10" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>424</v>
-      </c>
       <c r="G10" s="14" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H10" s="14" t="b">
         <v>1</v>
@@ -6354,22 +6354,22 @@
     </row>
     <row r="11" spans="1:9" ht="52" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
+        <v>424</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>425</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="F11" s="14" t="s">
         <v>426</v>
       </c>
-      <c r="D11" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="F11" s="14" t="s">
-        <v>427</v>
-      </c>
       <c r="G11" s="14" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H11" s="14" t="b">
         <v>1</v>
@@ -6380,25 +6380,25 @@
     </row>
     <row r="12" spans="1:9" ht="65" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
+        <v>456</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>457</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="C12" s="14" t="s">
         <v>458</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="D12" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E12" s="14" t="s">
         <v>459</v>
       </c>
-      <c r="D12" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="14" t="s">
+      <c r="F12" s="14" t="s">
         <v>460</v>
       </c>
-      <c r="F12" s="14" t="s">
-        <v>461</v>
-      </c>
       <c r="G12" s="14" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H12" s="14" t="b">
         <v>1</v>
@@ -6409,25 +6409,25 @@
     </row>
     <row r="13" spans="1:9" ht="64" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
+        <v>483</v>
+      </c>
+      <c r="B13" s="14" t="s">
         <v>484</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="C13" s="14" t="s">
+        <v>489</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>491</v>
+      </c>
+      <c r="F13" s="14" t="s">
         <v>485</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>490</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>419</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>492</v>
-      </c>
-      <c r="F13" s="14" t="s">
-        <v>486</v>
-      </c>
       <c r="G13" s="15" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H13" s="14" t="b">
         <v>1</v>
@@ -6438,25 +6438,25 @@
     </row>
     <row r="14" spans="1:9" ht="48" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
+        <v>486</v>
+      </c>
+      <c r="B14" s="14" t="s">
         <v>487</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="C14" s="14" t="s">
+        <v>490</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="F14" s="14" t="s">
         <v>488</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>491</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>493</v>
-      </c>
-      <c r="F14" s="14" t="s">
-        <v>489</v>
-      </c>
       <c r="G14" s="15" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H14" s="14" t="b">
         <v>1</v>
@@ -6486,22 +6486,22 @@
   <sheetData>
     <row r="1" spans="1:7" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
+        <v>429</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>430</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>385</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>431</v>
-      </c>
       <c r="F1" s="11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G1" s="11" t="s">
         <v>2</v>
@@ -6509,451 +6509,451 @@
     </row>
     <row r="2" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>431</v>
+      </c>
+      <c r="B2" t="s">
         <v>432</v>
       </c>
-      <c r="B2" t="s">
-        <v>433</v>
-      </c>
       <c r="C2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B3" t="s">
         <v>434</v>
       </c>
-      <c r="B3" t="s">
-        <v>435</v>
-      </c>
       <c r="C3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B4" t="s">
         <v>436</v>
       </c>
-      <c r="B4" t="s">
-        <v>437</v>
-      </c>
       <c r="C4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>437</v>
+      </c>
+      <c r="B5" t="s">
         <v>438</v>
       </c>
-      <c r="B5" t="s">
-        <v>439</v>
-      </c>
       <c r="C5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B6" t="s">
         <v>447</v>
       </c>
-      <c r="B6" t="s">
-        <v>448</v>
-      </c>
       <c r="C6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>495</v>
+      </c>
+      <c r="B7" t="s">
         <v>496</v>
       </c>
-      <c r="B7" t="s">
-        <v>497</v>
-      </c>
       <c r="C7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>448</v>
+      </c>
+      <c r="B8" t="s">
         <v>449</v>
       </c>
-      <c r="B8" t="s">
-        <v>450</v>
-      </c>
       <c r="C8" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>439</v>
+      </c>
+      <c r="B9" t="s">
         <v>440</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
+        <v>358</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" t="s">
-        <v>359</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>442</v>
-      </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>442</v>
+      </c>
+      <c r="B10" t="s">
         <v>443</v>
       </c>
-      <c r="B10" t="s">
-        <v>444</v>
-      </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>450</v>
+      </c>
+      <c r="B11" t="s">
         <v>451</v>
       </c>
-      <c r="B11" t="s">
-        <v>452</v>
-      </c>
       <c r="C11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>452</v>
+      </c>
+      <c r="B12" t="s">
         <v>453</v>
       </c>
-      <c r="B12" t="s">
-        <v>454</v>
-      </c>
       <c r="C12" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>497</v>
+      </c>
+      <c r="B13" t="s">
         <v>498</v>
       </c>
-      <c r="B13" t="s">
-        <v>499</v>
-      </c>
       <c r="C13" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>454</v>
+      </c>
+      <c r="B14" t="s">
         <v>455</v>
       </c>
-      <c r="B14" t="s">
-        <v>456</v>
-      </c>
       <c r="C14" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>444</v>
+      </c>
+      <c r="B15" t="s">
         <v>445</v>
       </c>
-      <c r="B15" t="s">
-        <v>446</v>
-      </c>
       <c r="C15" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>518</v>
+      </c>
+      <c r="B16" t="s">
+        <v>520</v>
+      </c>
+      <c r="C16" t="s">
+        <v>412</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B16" t="s">
-        <v>521</v>
-      </c>
-      <c r="C16" t="s">
-        <v>413</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>520</v>
-      </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>461</v>
+      </c>
+      <c r="B17" t="s">
         <v>462</v>
       </c>
-      <c r="B17" t="s">
-        <v>463</v>
-      </c>
       <c r="C17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>463</v>
+      </c>
+      <c r="B18" t="s">
         <v>464</v>
       </c>
-      <c r="B18" t="s">
-        <v>465</v>
-      </c>
       <c r="C18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>465</v>
+      </c>
+      <c r="B19" t="s">
         <v>466</v>
       </c>
-      <c r="B19" t="s">
-        <v>467</v>
-      </c>
       <c r="C19" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>467</v>
+      </c>
+      <c r="B20" t="s">
         <v>468</v>
       </c>
-      <c r="B20" t="s">
-        <v>469</v>
-      </c>
       <c r="C20" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>469</v>
+      </c>
+      <c r="B21" t="s">
         <v>470</v>
       </c>
-      <c r="B21" t="s">
-        <v>471</v>
-      </c>
       <c r="C21" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>471</v>
+      </c>
+      <c r="B22" t="s">
         <v>472</v>
       </c>
-      <c r="B22" t="s">
-        <v>473</v>
-      </c>
       <c r="C22" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>493</v>
+      </c>
+      <c r="B23" t="s">
         <v>494</v>
       </c>
-      <c r="B23" t="s">
-        <v>495</v>
-      </c>
       <c r="C23" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
   </sheetData>
